--- a/Output Datasets/Final Selected OTUs.xlsx
+++ b/Output Datasets/Final Selected OTUs.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="830">
   <si>
     <t>OTU</t>
   </si>
@@ -1217,1159 +1217,1291 @@
     <t>Otu1070</t>
   </si>
   <si>
-    <t>Oxalobacteraceae</t>
-  </si>
-  <si>
-    <t>Bifidobacteriaceae</t>
-  </si>
-  <si>
-    <t>Bacillaceae</t>
-  </si>
-  <si>
-    <t>Enterococcaceae</t>
-  </si>
-  <si>
-    <t>Ruminococcaceae</t>
-  </si>
-  <si>
-    <t>Porphyromonadaceae</t>
-  </si>
-  <si>
-    <t>Lachnospiraceae</t>
-  </si>
-  <si>
-    <t>Lactobacillaceae</t>
-  </si>
-  <si>
-    <t>Erysipelotrichaceae</t>
-  </si>
-  <si>
-    <t>Pseudomonadaceae</t>
-  </si>
-  <si>
-    <t>Sphingomonadaceae</t>
-  </si>
-  <si>
-    <t>Empty Cell</t>
-  </si>
-  <si>
-    <t>Staphylococcaceae</t>
-  </si>
-  <si>
-    <t>Moraxellaceae</t>
-  </si>
-  <si>
-    <t>Bacteroidaceae</t>
-  </si>
-  <si>
-    <t>Comamonadaceae</t>
-  </si>
-  <si>
-    <t>Streptococcaceae</t>
-  </si>
-  <si>
-    <t>Xanthomonadaceae</t>
-  </si>
-  <si>
-    <t>Methylophilaceae</t>
-  </si>
-  <si>
-    <t>Rikenellaceae</t>
-  </si>
-  <si>
-    <t>Alcaligenaceae</t>
-  </si>
-  <si>
-    <t>Unclassified</t>
-  </si>
-  <si>
-    <t>Veillonellaceae</t>
-  </si>
-  <si>
-    <t>Pseudonocardiaceae</t>
-  </si>
-  <si>
-    <t>Caulobacteraceae</t>
-  </si>
-  <si>
-    <t>Brevibacteriaceae</t>
-  </si>
-  <si>
-    <t>Burkholderiaceae</t>
-  </si>
-  <si>
-    <t>Intrasporangiaceae</t>
-  </si>
-  <si>
-    <t>Bradyrhizobiaceae</t>
-  </si>
-  <si>
-    <t>Hyphomicrobiaceae</t>
-  </si>
-  <si>
-    <t>Desulfovibrionaceae</t>
-  </si>
-  <si>
-    <t>Brucellaceae</t>
-  </si>
-  <si>
-    <t>Enterobacteriaceae</t>
-  </si>
-  <si>
-    <t>Corynebacteriaceae</t>
-  </si>
-  <si>
-    <t>Thermoactinomycetaceae</t>
-  </si>
-  <si>
-    <t>Sphingobacteriaceae</t>
-  </si>
-  <si>
-    <t>Mycobacteriaceae</t>
-  </si>
-  <si>
-    <t>Prevotellaceae</t>
-  </si>
-  <si>
-    <t>Phyllobacteriaceae</t>
-  </si>
-  <si>
-    <t>Coriobacteriaceae</t>
-  </si>
-  <si>
-    <t>Rhodobacteraceae</t>
-  </si>
-  <si>
-    <t>Actinomycetaceae</t>
-  </si>
-  <si>
-    <t>Defluviitaleaceae</t>
-  </si>
-  <si>
-    <t>Thermomonosporaceae</t>
-  </si>
-  <si>
-    <t>Nocardiopsaceae</t>
-  </si>
-  <si>
-    <t>Sphaerobacteraceae</t>
-  </si>
-  <si>
-    <t>Planococcaceae</t>
-  </si>
-  <si>
-    <t>Nocardioidaceae</t>
-  </si>
-  <si>
-    <t>Fusobacteriaceae</t>
-  </si>
-  <si>
-    <t>Streptomycetaceae</t>
-  </si>
-  <si>
-    <t>Dermacoccaceae</t>
-  </si>
-  <si>
-    <t>Microbacteriaceae</t>
-  </si>
-  <si>
-    <t>Flavobacteriaceae</t>
-  </si>
-  <si>
-    <t>Christensenellaceae</t>
-  </si>
-  <si>
-    <t>Rhodocyclaceae</t>
-  </si>
-  <si>
-    <t>Erythrobacteraceae</t>
-  </si>
-  <si>
-    <t>Acidaminococcaceae</t>
-  </si>
-  <si>
-    <t>Carnobacteriaceae</t>
-  </si>
-  <si>
-    <t>Leptotrichiaceae</t>
-  </si>
-  <si>
-    <t>Neisseriaceae</t>
-  </si>
-  <si>
-    <t>Nocardiaceae</t>
-  </si>
-  <si>
-    <t>Pasteurellaceae</t>
-  </si>
-  <si>
-    <t>Synergistaceae</t>
-  </si>
-  <si>
-    <t>Micrococcaceae</t>
-  </si>
-  <si>
-    <t>Paenibacillaceae</t>
-  </si>
-  <si>
-    <t>Bacteriovoracaceae</t>
-  </si>
-  <si>
-    <t>Rhizobiaceae</t>
-  </si>
-  <si>
-    <t>Bdellovibrionaceae</t>
-  </si>
-  <si>
-    <t>Acetobacteraceae</t>
-  </si>
-  <si>
-    <t>Cytophagaceae</t>
-  </si>
-  <si>
-    <t>Sandaracinaceae</t>
-  </si>
-  <si>
-    <t>Pseudoalteromonadaceae</t>
-  </si>
-  <si>
-    <t>Rhodobiaceae</t>
-  </si>
-  <si>
-    <t>Phycisphaeraceae</t>
-  </si>
-  <si>
-    <t>Hyphomonadaceae</t>
-  </si>
-  <si>
-    <t>Alteromonadaceae</t>
-  </si>
-  <si>
-    <t>Haloplasmataceae</t>
-  </si>
-  <si>
-    <t>Anaerolineaceae</t>
-  </si>
-  <si>
-    <t>Trueperaceae</t>
-  </si>
-  <si>
-    <t>Patulibacteraceae</t>
-  </si>
-  <si>
-    <t>Coxiellaceae</t>
-  </si>
-  <si>
-    <t>Planctomycetaceae</t>
-  </si>
-  <si>
-    <t>Caldilineaceae</t>
-  </si>
-  <si>
-    <t>Rickettsiaceae</t>
-  </si>
-  <si>
-    <t>Eubacteriaceae</t>
-  </si>
-  <si>
-    <t>Oceanospirillaceae</t>
-  </si>
-  <si>
-    <t>Deinococcaceae</t>
-  </si>
-  <si>
-    <t>Alcanivoracaceae</t>
-  </si>
-  <si>
-    <t>Parachlamydiaceae</t>
-  </si>
-  <si>
-    <t>Acidimicrobiaceae</t>
-  </si>
-  <si>
-    <t>Streptosporangiaceae</t>
-  </si>
-  <si>
-    <t>Peptococcaceae</t>
-  </si>
-  <si>
-    <t>Chromatiaceae</t>
-  </si>
-  <si>
-    <t>Peptostreptococcaceae</t>
-  </si>
-  <si>
-    <t>Herbaspirillum</t>
-  </si>
-  <si>
-    <t>Bifidobacterium</t>
-  </si>
-  <si>
-    <t>Bacillus</t>
-  </si>
-  <si>
-    <t>Enterococcus</t>
-  </si>
-  <si>
-    <t>Ruminococcus</t>
-  </si>
-  <si>
-    <t>Parabacteroides</t>
-  </si>
-  <si>
-    <t>Lactobacillus</t>
-  </si>
-  <si>
-    <t>Lachnospira</t>
-  </si>
-  <si>
-    <t>Catenibacterium</t>
-  </si>
-  <si>
-    <t>Pseudomonas</t>
-  </si>
-  <si>
-    <t>Sphingomonas</t>
-  </si>
-  <si>
-    <t>Undibacterium</t>
-  </si>
-  <si>
-    <t>Roseburia</t>
-  </si>
-  <si>
-    <t>Subdoligranulum</t>
-  </si>
-  <si>
-    <t>Staphylococcus</t>
-  </si>
-  <si>
-    <t>Acinetobacter</t>
-  </si>
-  <si>
-    <t>Bacteroides</t>
-  </si>
-  <si>
-    <t>Curvibacter</t>
-  </si>
-  <si>
-    <t>Streptococcus</t>
-  </si>
-  <si>
-    <t>Stenotrophomonas</t>
-  </si>
-  <si>
-    <t>Anaerosporobacter</t>
-  </si>
-  <si>
-    <t>Dorea</t>
-  </si>
-  <si>
-    <t>Alistipes</t>
-  </si>
-  <si>
-    <t>Pseudobutyrivibrio</t>
-  </si>
-  <si>
-    <t>Sutterella</t>
-  </si>
-  <si>
-    <t>Pelomonas</t>
-  </si>
-  <si>
-    <t>Veillonella</t>
-  </si>
-  <si>
-    <t>Pseudonocardia</t>
-  </si>
-  <si>
-    <t>Brevibacterium</t>
-  </si>
-  <si>
-    <t>Methylophilus</t>
-  </si>
-  <si>
-    <t>Megasphaera</t>
-  </si>
-  <si>
-    <t>Burkholderia</t>
-  </si>
-  <si>
-    <t>Anaerostipes</t>
-  </si>
-  <si>
-    <t>Ralstonia</t>
-  </si>
-  <si>
-    <t>Janibacter</t>
-  </si>
-  <si>
-    <t>Desulfovibrio</t>
-  </si>
-  <si>
-    <t>Ochrobactrum</t>
-  </si>
-  <si>
-    <t>Serratia</t>
-  </si>
-  <si>
-    <t>Corynebacterium</t>
-  </si>
-  <si>
-    <t>Planifilum</t>
-  </si>
-  <si>
-    <t>Parapedobacter</t>
-  </si>
-  <si>
-    <t>Mycobacterium</t>
-  </si>
-  <si>
-    <t>Blautia</t>
-  </si>
-  <si>
-    <t>Prevotella</t>
-  </si>
-  <si>
-    <t>Mesorhizobium</t>
-  </si>
-  <si>
-    <t>Tabrizicola</t>
-  </si>
-  <si>
-    <t>Actinomyces</t>
-  </si>
-  <si>
-    <t>Thermobispora</t>
-  </si>
-  <si>
-    <t>Thermobifida</t>
-  </si>
-  <si>
-    <t>Coprococcus</t>
-  </si>
-  <si>
-    <t>Mogibacterium</t>
-  </si>
-  <si>
-    <t>Sphaerobacter</t>
-  </si>
-  <si>
-    <t>Lysinibacillus</t>
-  </si>
-  <si>
-    <t>Marmoricola</t>
-  </si>
-  <si>
-    <t>Providencia</t>
-  </si>
-  <si>
-    <t>Slackia</t>
-  </si>
-  <si>
-    <t>Fusobacterium</t>
-  </si>
-  <si>
-    <t>Streptomyces</t>
-  </si>
-  <si>
-    <t>Butyricimonas</t>
-  </si>
-  <si>
-    <t>Dermacoccus</t>
-  </si>
-  <si>
-    <t>Allobaculum</t>
-  </si>
-  <si>
-    <t>Leucobacter</t>
-  </si>
-  <si>
-    <t>Flavobacterium</t>
-  </si>
-  <si>
-    <t>Sulfuritalea</t>
-  </si>
-  <si>
-    <t>Pseudoxanthomonas</t>
-  </si>
-  <si>
-    <t>Mitsuokella</t>
-  </si>
-  <si>
-    <t>Hydrogenophaga</t>
-  </si>
-  <si>
-    <t>Nevskia</t>
-  </si>
-  <si>
-    <t>Phascolarctobacterium</t>
-  </si>
-  <si>
-    <t>Dolosigranulum</t>
-  </si>
-  <si>
-    <t>Dialister</t>
-  </si>
-  <si>
-    <t>Leptotrichia</t>
-  </si>
-  <si>
-    <t>Coprobacter</t>
-  </si>
-  <si>
-    <t>Rhodococcus</t>
-  </si>
-  <si>
-    <t>Acidaminococcus</t>
-  </si>
-  <si>
-    <t>Olsenella</t>
-  </si>
-  <si>
-    <t>Devosia</t>
-  </si>
-  <si>
-    <t>Haemophilus</t>
-  </si>
-  <si>
-    <t>Rubellimicrobium</t>
-  </si>
-  <si>
-    <t>Cloacibacillus</t>
-  </si>
-  <si>
-    <t>Hydrocarboniphaga</t>
-  </si>
-  <si>
-    <t>Nesterenkonia</t>
-  </si>
-  <si>
-    <t>Paludibacter</t>
-  </si>
-  <si>
-    <t>Capnocytophaga</t>
-  </si>
-  <si>
-    <t>Adlercreutzia</t>
-  </si>
-  <si>
-    <t>Thermobacillus</t>
-  </si>
-  <si>
-    <t>Barnesiella</t>
-  </si>
-  <si>
-    <t>Peredibacter</t>
-  </si>
-  <si>
-    <t>Methylibium</t>
-  </si>
-  <si>
-    <t>Bordetella</t>
-  </si>
-  <si>
-    <t>Enterorhabdus</t>
-  </si>
-  <si>
-    <t>Papillibacter</t>
-  </si>
-  <si>
-    <t>Varibaculum</t>
-  </si>
-  <si>
-    <t>Bilophila</t>
-  </si>
-  <si>
-    <t>Cloacibacterium</t>
-  </si>
-  <si>
-    <t>Ornithinicoccus</t>
-  </si>
-  <si>
-    <t>Sphingobacterium</t>
-  </si>
-  <si>
-    <t>Chryseobacterium</t>
-  </si>
-  <si>
-    <t>Anaerococcus</t>
-  </si>
-  <si>
-    <t>Rhizobium</t>
-  </si>
-  <si>
-    <t>Achromobacter</t>
-  </si>
-  <si>
-    <t>Brevundimonas</t>
-  </si>
-  <si>
-    <t>Bdellovibrio</t>
-  </si>
-  <si>
-    <t>Paraprevotella</t>
-  </si>
-  <si>
-    <t>Roseomonas</t>
-  </si>
-  <si>
-    <t>Actinomadura</t>
-  </si>
-  <si>
-    <t>Oscillibacter</t>
-  </si>
-  <si>
-    <t>Candidimonas</t>
-  </si>
-  <si>
-    <t>Azohydromonas</t>
-  </si>
-  <si>
-    <t>Lachnoanaerobaculum</t>
-  </si>
-  <si>
-    <t>Zoogloea</t>
-  </si>
-  <si>
-    <t>Lysobacter</t>
-  </si>
-  <si>
-    <t>Pannonibacter</t>
-  </si>
-  <si>
-    <t>Taibaiella</t>
-  </si>
-  <si>
-    <t>Paenibacillus</t>
-  </si>
-  <si>
-    <t>Sporosarcina</t>
-  </si>
-  <si>
-    <t>Geminicoccus</t>
-  </si>
-  <si>
-    <t>Pseudoalteromonas</t>
-  </si>
-  <si>
-    <t>Nocardioides</t>
-  </si>
-  <si>
-    <t>Porphyromonas</t>
-  </si>
-  <si>
-    <t>Rhodoligotrophos</t>
-  </si>
-  <si>
-    <t>Anaerofilum</t>
-  </si>
-  <si>
-    <t>Hirschia</t>
-  </si>
-  <si>
-    <t>Altererythrobacter</t>
-  </si>
-  <si>
-    <t>Alloprevotella</t>
-  </si>
-  <si>
-    <t>Simiduia</t>
-  </si>
-  <si>
-    <t>Haloplasma</t>
-  </si>
-  <si>
-    <t>Pedomicrobium</t>
-  </si>
-  <si>
-    <t>Hydrotalea</t>
-  </si>
-  <si>
-    <t>Truepera</t>
-  </si>
-  <si>
-    <t>Patulibacter</t>
-  </si>
-  <si>
-    <t>Aquicella</t>
-  </si>
-  <si>
-    <t>Oxalobacter</t>
-  </si>
-  <si>
-    <t>Alloiococcus</t>
-  </si>
-  <si>
-    <t>Nordella</t>
-  </si>
-  <si>
-    <t>Phocaeicola</t>
-  </si>
-  <si>
-    <t>Eubacterium</t>
-  </si>
-  <si>
-    <t>Aquincola</t>
-  </si>
-  <si>
-    <t>Anaerotruncus</t>
-  </si>
-  <si>
-    <t>Pseudospirillum</t>
-  </si>
-  <si>
-    <t>Thermomonas</t>
-  </si>
-  <si>
-    <t>Deinococcus</t>
-  </si>
-  <si>
-    <t>Pedobacter</t>
-  </si>
-  <si>
-    <t>Nitrospira</t>
-  </si>
-  <si>
-    <t>Alcanivorax</t>
-  </si>
-  <si>
-    <t>Thermocrispum</t>
-  </si>
-  <si>
-    <t>Candidatus_Protochlamydia</t>
-  </si>
-  <si>
-    <t>Intestinimonas</t>
-  </si>
-  <si>
-    <t>Nonomuraea</t>
-  </si>
-  <si>
-    <t>Nostoc</t>
-  </si>
-  <si>
-    <t>Parasutterella</t>
-  </si>
-  <si>
-    <t>Tatumella</t>
-  </si>
-  <si>
-    <t>Rheinheimera</t>
-  </si>
-  <si>
-    <t>Neisseria</t>
-  </si>
-  <si>
-    <t>Synechococcus</t>
-  </si>
-  <si>
-    <t>Herbaspirillum_huttiense</t>
-  </si>
-  <si>
-    <t>Enterococcus_durans</t>
-  </si>
-  <si>
-    <t>Parabacteroides_distasonis</t>
-  </si>
-  <si>
-    <t>Pseudomonas_azotoformans</t>
-  </si>
-  <si>
-    <t>Sphingomonas_paucimobilis</t>
-  </si>
-  <si>
-    <t>Undibacterium_pigrum</t>
-  </si>
-  <si>
-    <t>Staphylococcus_sciuri</t>
-  </si>
-  <si>
-    <t>Acinetobacter_guillouiae</t>
-  </si>
-  <si>
-    <t>[Clostridium]_innocuum</t>
-  </si>
-  <si>
-    <t>Bacteroides_uniformis</t>
-  </si>
-  <si>
-    <t>Streptococcus_parasanguinis</t>
-  </si>
-  <si>
-    <t>Bacteroides_vulgatus_ATCC_8482</t>
-  </si>
-  <si>
-    <t>Streptococcus_pyogenes</t>
-  </si>
-  <si>
-    <t>unidentified</t>
-  </si>
-  <si>
-    <t>Alistipes_onderdonkii_DSM_19147</t>
-  </si>
-  <si>
-    <t>human_gut_metagenome</t>
-  </si>
-  <si>
-    <t>Eubacterium_rectale_ATCC_33656</t>
-  </si>
-  <si>
-    <t>Bacteroides_thetaiotaomicron</t>
-  </si>
-  <si>
-    <t>Clostridium_perfringens_NCTC_8239</t>
-  </si>
-  <si>
-    <t>Pseudonocardia_zijingensis</t>
-  </si>
-  <si>
-    <t>Oryza_sativa_Japonica_Group</t>
-  </si>
-  <si>
-    <t>Brevibacterium_casei</t>
-  </si>
-  <si>
-    <t>Bacteroides_ovatus</t>
-  </si>
-  <si>
-    <t>Burkholderia_caledonica</t>
-  </si>
-  <si>
-    <t>Acinetobacter_calcoaceticus</t>
-  </si>
-  <si>
-    <t>Ralstonia_pickettii</t>
-  </si>
-  <si>
-    <t>Desulfovibrio_piger</t>
-  </si>
-  <si>
-    <t>Ochrobactrum_intermedium</t>
-  </si>
-  <si>
-    <t>Clostridiales_bacterium_VE202-14</t>
-  </si>
-  <si>
-    <t>Ruminococcus_sp._80/3</t>
-  </si>
-  <si>
-    <t>Serratia_marcescens</t>
-  </si>
-  <si>
-    <t>Corynebacterium_macginleyi</t>
-  </si>
-  <si>
-    <t>wallaby_gut_metagenome</t>
-  </si>
-  <si>
-    <t>Staphylococcus_capitis</t>
-  </si>
-  <si>
-    <t>Clostridiales_bacterium_VE202-16</t>
-  </si>
-  <si>
-    <t>Clostridiales_bacterium_canine_oral_taxon_085</t>
-  </si>
-  <si>
-    <t>Prevotella_sp._DJF_LS16</t>
-  </si>
-  <si>
-    <t>Mesorhizobium_amorphae</t>
-  </si>
-  <si>
-    <t>Olsenella_sp._SK9K4</t>
-  </si>
-  <si>
-    <t>Clostridium_butyricum</t>
-  </si>
-  <si>
-    <t>Bacteroides_caccae</t>
-  </si>
-  <si>
-    <t>Actinomyces_odontolyticus</t>
-  </si>
-  <si>
-    <t>Parabacteroides_merdae</t>
-  </si>
-  <si>
-    <t>Thermobispora_bispora</t>
-  </si>
-  <si>
-    <t>Megasphaera_elsdenii</t>
-  </si>
-  <si>
-    <t>Ruminococcus_sp._16442</t>
-  </si>
-  <si>
-    <t>Thermobifida_fusca</t>
-  </si>
-  <si>
-    <t>Ruminococcus_sp._5_1_39BFAA</t>
-  </si>
-  <si>
-    <t>butyrate-producing_bacterium_L2-50</t>
-  </si>
-  <si>
-    <t>Eubacterium_eligens_ATCC_27750</t>
-  </si>
-  <si>
-    <t>Lysinibacillus_massiliensis</t>
-  </si>
-  <si>
-    <t>Providencia_rettgeri</t>
-  </si>
-  <si>
-    <t>Bacteroides_massiliensis</t>
-  </si>
-  <si>
-    <t>Slackia_piriformis</t>
-  </si>
-  <si>
-    <t>Fusobacterium_nucleatum</t>
-  </si>
-  <si>
-    <t>Streptomyces_thermovulgaris</t>
-  </si>
-  <si>
-    <t>Dermacoccus_profundi</t>
-  </si>
-  <si>
-    <t>Parabacteroides_goldsteinii</t>
-  </si>
-  <si>
-    <t>Eubacterium_ventriosum</t>
-  </si>
-  <si>
-    <t>Clostridium_scindens</t>
-  </si>
-  <si>
-    <t>Lactobacillus_fermentum</t>
-  </si>
-  <si>
-    <t>bioreactor_metagenome</t>
-  </si>
-  <si>
-    <t>Pseudoxanthomonas_mexicana</t>
-  </si>
-  <si>
-    <t>Actinomyces_graevenitzii</t>
-  </si>
-  <si>
-    <t>Arabidopsis_thaliana_(thale_cress)</t>
-  </si>
-  <si>
-    <t>Leptotrichia_hofstadii</t>
-  </si>
-  <si>
-    <t>Lactobacillus_intestinalis</t>
-  </si>
-  <si>
-    <t>Fusobacterium_varium</t>
-  </si>
-  <si>
-    <t>Fusicatenibacter_saccharivorans</t>
-  </si>
-  <si>
-    <t>Prevotella_buccae</t>
-  </si>
-  <si>
-    <t>Alistipes_indistinctus_YIT_12060</t>
-  </si>
-  <si>
-    <t>Coriobacteriaceae_bacterium_JC110</t>
-  </si>
-  <si>
-    <t>Rhodococcus_corynebacterioides</t>
-  </si>
-  <si>
-    <t>Haemophilus_parainfluenzae</t>
-  </si>
-  <si>
-    <t>Clostridium_sp._ATCC_29733</t>
-  </si>
-  <si>
-    <t>Lachnospiraceae_bacterium_19gly4</t>
-  </si>
-  <si>
-    <t>Hydrocarboniphaga_daqingensis</t>
-  </si>
-  <si>
-    <t>Bacteroidetes_oral_taxon_274_str._F0058</t>
-  </si>
-  <si>
-    <t>Streptomyces_avidinii</t>
-  </si>
-  <si>
-    <t>Clostridiaceae_bacterium_JC13</t>
-  </si>
-  <si>
-    <t>Lactobacillus_casei</t>
-  </si>
-  <si>
-    <t>bacterium_Eza8</t>
-  </si>
-  <si>
-    <t>Varibaculum_cambriense</t>
-  </si>
-  <si>
-    <t>unidentified_rumen_bacterium_RFN71</t>
-  </si>
-  <si>
-    <t>Streptococcus_anginosus</t>
-  </si>
-  <si>
-    <t>Bilophila_wadsworthia</t>
-  </si>
-  <si>
-    <t>butyrate-producing_bacterium_SS3/4</t>
-  </si>
-  <si>
-    <t>Haemophilus_influenzae</t>
-  </si>
-  <si>
-    <t>Sphingobacterium_multivorum</t>
-  </si>
-  <si>
-    <t>Bacteroides_plebeius</t>
-  </si>
-  <si>
-    <t>Rhodococcus_fascians</t>
-  </si>
-  <si>
-    <t>Rhizobium_sp._CC-LY845</t>
-  </si>
-  <si>
-    <t>Streptococcus_salivarius</t>
-  </si>
-  <si>
-    <t>Brevundimonas_diminuta</t>
-  </si>
-  <si>
-    <t>[Eubacterium]_cylindroides</t>
-  </si>
-  <si>
-    <t>Paraprevotella_xylaniphila</t>
-  </si>
-  <si>
-    <t>Roseomonas_mucosa</t>
-  </si>
-  <si>
-    <t>Oscillibacter_ruminantium_GH1</t>
-  </si>
-  <si>
-    <t>Achromobacter_sp._MTCC_11931</t>
-  </si>
-  <si>
-    <t>Zoogloea_resiniphila</t>
-  </si>
-  <si>
-    <t>Bacillus_beringensis</t>
-  </si>
-  <si>
-    <t>Spartobacteria_bacterium_Gsoil_144</t>
-  </si>
-  <si>
-    <t>Paenibacillus_timonensis</t>
-  </si>
-  <si>
-    <t>Desulfovibrio_simplex</t>
-  </si>
-  <si>
-    <t>Clostridium_sp._CAG:306</t>
-  </si>
-  <si>
-    <t>Leptotrichia_sp._oral_clone_IK040</t>
-  </si>
-  <si>
-    <t>Flavobacterium_ummariense</t>
-  </si>
-  <si>
-    <t>alpha_proteobacterium_S22-37</t>
-  </si>
-  <si>
-    <t>Lactobacillus_agilis</t>
-  </si>
-  <si>
-    <t>Alloprevotella_tannerae</t>
-  </si>
-  <si>
-    <t>Physcomitrella_patens</t>
-  </si>
-  <si>
-    <t>Sediminibacterium_sp._MIC4028</t>
-  </si>
-  <si>
-    <t>Patulibacter_minatonensis</t>
-  </si>
-  <si>
-    <t>Oxalobacter_formigenes</t>
-  </si>
-  <si>
-    <t>Streptomyces_sp._A404_Ydz-QZ</t>
-  </si>
-  <si>
-    <t>Flavobacterium_cucumis</t>
-  </si>
-  <si>
-    <t>Prevotella_nigrescens</t>
-  </si>
-  <si>
-    <t>bacterium_enrichment_culture_clone_heteroC6_4W</t>
-  </si>
-  <si>
-    <t>Lactobacillus_paralimentarius</t>
-  </si>
-  <si>
-    <t>Deinococcus_grandis</t>
-  </si>
-  <si>
-    <t>Pedobacter_heparinus_DSM_2366</t>
-  </si>
-  <si>
-    <t>Thermocrispum_municipale</t>
-  </si>
-  <si>
-    <t>Thermobacillus_composti_KWC4</t>
-  </si>
-  <si>
-    <t>bacterium_R2</t>
-  </si>
-  <si>
-    <t>Niastella_sp._HME8655</t>
-  </si>
-  <si>
-    <t>Sutterella_parvirubra</t>
-  </si>
-  <si>
-    <t>Flavobacterium_marinum</t>
-  </si>
-  <si>
-    <t>Nostoc_commune</t>
-  </si>
-  <si>
-    <t>Ruminococcus_gnavus_CC55_001C</t>
-  </si>
-  <si>
-    <t>Eubacterium_siraeum_DSM_15702</t>
-  </si>
-  <si>
-    <t>Xanthomonas_sp._NBRC_14591</t>
-  </si>
-  <si>
-    <t>Rosenbergiella_nectarea</t>
-  </si>
-  <si>
-    <t>[Eubacterium]_dolichum</t>
-  </si>
-  <si>
-    <t>Phascolarctobacterium_faecium</t>
-  </si>
-  <si>
-    <t>Clostridium_bartlettii_DSM_16795</t>
-  </si>
-  <si>
-    <t>Blautia_producta</t>
+    <t>F_Oxalobacteraceae</t>
+  </si>
+  <si>
+    <t>F_Bifidobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Bacillaceae</t>
+  </si>
+  <si>
+    <t>F_Enterococcaceae</t>
+  </si>
+  <si>
+    <t>F_Ruminococcaceae</t>
+  </si>
+  <si>
+    <t>F_Porphyromonadaceae</t>
+  </si>
+  <si>
+    <t>F_Lachnospiraceae</t>
+  </si>
+  <si>
+    <t>F_Lactobacillaceae</t>
+  </si>
+  <si>
+    <t>F_Erysipelotrichaceae</t>
+  </si>
+  <si>
+    <t>F_Pseudomonadaceae</t>
+  </si>
+  <si>
+    <t>F_Sphingomonadaceae</t>
+  </si>
+  <si>
+    <t>C_Gemmatimonadetes_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Staphylococcaceae</t>
+  </si>
+  <si>
+    <t>F_Moraxellaceae</t>
+  </si>
+  <si>
+    <t>F_Bacteroidaceae</t>
+  </si>
+  <si>
+    <t>F_Comamonadaceae</t>
+  </si>
+  <si>
+    <t>F_Streptococcaceae</t>
+  </si>
+  <si>
+    <t>F_Xanthomonadaceae</t>
+  </si>
+  <si>
+    <t>F_Methylophilaceae</t>
+  </si>
+  <si>
+    <t>F_Rikenellaceae</t>
+  </si>
+  <si>
+    <t>F_Alcaligenaceae</t>
+  </si>
+  <si>
+    <t>O_Bacteroidales_Unclassified</t>
+  </si>
+  <si>
+    <t>O_Clostridiales_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Veillonellaceae</t>
+  </si>
+  <si>
+    <t>C_Actinobacteria_Unclassified</t>
+  </si>
+  <si>
+    <t>P_Cyanobacteria_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Caulobacteraceae</t>
+  </si>
+  <si>
+    <t>P_Firmicutes_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Burkholderiaceae</t>
+  </si>
+  <si>
+    <t>F_Bradyrhizobiaceae</t>
+  </si>
+  <si>
+    <t>F_Hyphomicrobiaceae</t>
+  </si>
+  <si>
+    <t>F_Desulfovibrionaceae</t>
+  </si>
+  <si>
+    <t>F_Brucellaceae</t>
+  </si>
+  <si>
+    <t>C_Thermomicrobia_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Enterobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Thermoactinomycetaceae</t>
+  </si>
+  <si>
+    <t>O_Rhizobiales_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Sphingobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Prevotellaceae</t>
+  </si>
+  <si>
+    <t>F_Phyllobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Coriobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Rhodobacteraceae</t>
+  </si>
+  <si>
+    <t>F_Actinomycetaceae</t>
+  </si>
+  <si>
+    <t>F_Defluviitaleaceae</t>
+  </si>
+  <si>
+    <t>F_Sphaerobacteraceae</t>
+  </si>
+  <si>
+    <t>F_Planococcaceae</t>
+  </si>
+  <si>
+    <t>O_Myxococcales_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Fusobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Flavobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Christensenellaceae</t>
+  </si>
+  <si>
+    <t>F_Rhodocyclaceae</t>
+  </si>
+  <si>
+    <t>O_Rickettsiales_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Erythrobacteraceae</t>
+  </si>
+  <si>
+    <t>O_Xanthomonadales_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Acidaminococcaceae</t>
+  </si>
+  <si>
+    <t>F_Carnobacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Leptotrichiaceae</t>
+  </si>
+  <si>
+    <t>F_Neisseriaceae</t>
+  </si>
+  <si>
+    <t>F_Pasteurellaceae</t>
+  </si>
+  <si>
+    <t>K_Bacteria_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Synergistaceae</t>
+  </si>
+  <si>
+    <t>F_Paenibacillaceae</t>
+  </si>
+  <si>
+    <t>F_Bacteriovoracaceae</t>
+  </si>
+  <si>
+    <t>C_Bacilli_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Rhizobiaceae</t>
+  </si>
+  <si>
+    <t>F_Bdellovibrionaceae</t>
+  </si>
+  <si>
+    <t>F_Acetobacteraceae</t>
+  </si>
+  <si>
+    <t>O_Rhodospirillales_Unclassified</t>
+  </si>
+  <si>
+    <t>O_Bacillales_Unclassified</t>
+  </si>
+  <si>
+    <t>C_Spartobacteria_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Cytophagaceae</t>
+  </si>
+  <si>
+    <t>O_Sphingobacteriales_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Sandaracinaceae</t>
+  </si>
+  <si>
+    <t>O_Acidimicrobiales_Unclassified</t>
+  </si>
+  <si>
+    <t>O_Solirubrobacterales_Unclassified</t>
+  </si>
+  <si>
+    <t>C_Alphaproteobacteria_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Pseudoalteromonadaceae</t>
+  </si>
+  <si>
+    <t>F_Rhodobiaceae</t>
+  </si>
+  <si>
+    <t>F_Phycisphaeraceae</t>
+  </si>
+  <si>
+    <t>F_Hyphomonadaceae</t>
+  </si>
+  <si>
+    <t>F_Alteromonadaceae</t>
+  </si>
+  <si>
+    <t>F_Haloplasmataceae</t>
+  </si>
+  <si>
+    <t>F_Anaerolineaceae</t>
+  </si>
+  <si>
+    <t>F_Trueperaceae</t>
+  </si>
+  <si>
+    <t>F_Patulibacteraceae</t>
+  </si>
+  <si>
+    <t>F_Coxiellaceae</t>
+  </si>
+  <si>
+    <t>P_Chlamydiae_Unclassified</t>
+  </si>
+  <si>
+    <t>P_Planctomycetes_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Caldilineaceae</t>
+  </si>
+  <si>
+    <t>F_Rickettsiaceae</t>
+  </si>
+  <si>
+    <t>P_Chlorobi_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Eubacteriaceae</t>
+  </si>
+  <si>
+    <t>F_Oceanospirillaceae</t>
+  </si>
+  <si>
+    <t>F_Deinococcaceae</t>
+  </si>
+  <si>
+    <t>O_Nitrospirales_Unclassified</t>
+  </si>
+  <si>
+    <t>C_Elusimicrobia_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Alcanivoracaceae</t>
+  </si>
+  <si>
+    <t>F_Acidimicrobiaceae</t>
+  </si>
+  <si>
+    <t>F_Peptococcaceae</t>
+  </si>
+  <si>
+    <t>C_Mollicutes_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Chromatiaceae</t>
+  </si>
+  <si>
+    <t>F_Peptostreptococcaceae</t>
+  </si>
+  <si>
+    <t>G_Herbaspirillum</t>
+  </si>
+  <si>
+    <t>G_Bifidobacterium</t>
+  </si>
+  <si>
+    <t>G_Bacillus</t>
+  </si>
+  <si>
+    <t>G_Enterococcus</t>
+  </si>
+  <si>
+    <t>G_Ruminococcus</t>
+  </si>
+  <si>
+    <t>G_Parabacteroides</t>
+  </si>
+  <si>
+    <t>F_Lachnospiraceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Lactobacillus</t>
+  </si>
+  <si>
+    <t>G_Lachnospira</t>
+  </si>
+  <si>
+    <t>G_Catenibacterium</t>
+  </si>
+  <si>
+    <t>G_Pseudomonas</t>
+  </si>
+  <si>
+    <t>G_Sphingomonas</t>
+  </si>
+  <si>
+    <t>F_Ruminococcaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Undibacterium</t>
+  </si>
+  <si>
+    <t>G_Roseburia</t>
+  </si>
+  <si>
+    <t>G_Subdoligranulum</t>
+  </si>
+  <si>
+    <t>G_Staphylococcus</t>
+  </si>
+  <si>
+    <t>G_Acinetobacter</t>
+  </si>
+  <si>
+    <t>F_Erysipelotrichaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Bacteroides</t>
+  </si>
+  <si>
+    <t>G_Curvibacter</t>
+  </si>
+  <si>
+    <t>G_Streptococcus</t>
+  </si>
+  <si>
+    <t>G_Stenotrophomonas</t>
+  </si>
+  <si>
+    <t>G_Anaerosporobacter</t>
+  </si>
+  <si>
+    <t>G_Dorea</t>
+  </si>
+  <si>
+    <t>F_Methylophilaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Alistipes</t>
+  </si>
+  <si>
+    <t>G_Pseudobutyrivibrio</t>
+  </si>
+  <si>
+    <t>G_Sutterella</t>
+  </si>
+  <si>
+    <t>G_Pelomonas</t>
+  </si>
+  <si>
+    <t>G_Veillonella</t>
+  </si>
+  <si>
+    <t>F_Caulobacteraceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Methylophilus</t>
+  </si>
+  <si>
+    <t>G_Megasphaera</t>
+  </si>
+  <si>
+    <t>G_Burkholderia</t>
+  </si>
+  <si>
+    <t>G_Anaerostipes</t>
+  </si>
+  <si>
+    <t>G_Ralstonia</t>
+  </si>
+  <si>
+    <t>F_Bradyrhizobiaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Hyphomicrobiaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Desulfovibrio</t>
+  </si>
+  <si>
+    <t>G_Ochrobactrum</t>
+  </si>
+  <si>
+    <t>G_Serratia</t>
+  </si>
+  <si>
+    <t>G_Planifilum</t>
+  </si>
+  <si>
+    <t>G_Parapedobacter</t>
+  </si>
+  <si>
+    <t>G_Blautia</t>
+  </si>
+  <si>
+    <t>G_Prevotella</t>
+  </si>
+  <si>
+    <t>G_Mesorhizobium</t>
+  </si>
+  <si>
+    <t>F_Coriobacteriaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Tabrizicola</t>
+  </si>
+  <si>
+    <t>G_Actinomyces</t>
+  </si>
+  <si>
+    <t>F_Defluviitaleaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Phyllobacteriaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Coprococcus</t>
+  </si>
+  <si>
+    <t>G_Sphaerobacter</t>
+  </si>
+  <si>
+    <t>G_Lysinibacillus</t>
+  </si>
+  <si>
+    <t>G_Providencia</t>
+  </si>
+  <si>
+    <t>G_Slackia</t>
+  </si>
+  <si>
+    <t>G_Fusobacterium</t>
+  </si>
+  <si>
+    <t>G_Butyricimonas</t>
+  </si>
+  <si>
+    <t>G_Allobaculum</t>
+  </si>
+  <si>
+    <t>G_Flavobacterium</t>
+  </si>
+  <si>
+    <t>F_Christensenellaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Sulfuritalea</t>
+  </si>
+  <si>
+    <t>G_Pseudoxanthomonas</t>
+  </si>
+  <si>
+    <t>G_Mitsuokella</t>
+  </si>
+  <si>
+    <t>F_Erythrobacteraceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Hydrogenophaga</t>
+  </si>
+  <si>
+    <t>G_Phascolarctobacterium</t>
+  </si>
+  <si>
+    <t>G_Dolosigranulum</t>
+  </si>
+  <si>
+    <t>G_Dialister</t>
+  </si>
+  <si>
+    <t>G_Leptotrichia</t>
+  </si>
+  <si>
+    <t>F_Neisseriaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Coprobacter</t>
+  </si>
+  <si>
+    <t>G_Acidaminococcus</t>
+  </si>
+  <si>
+    <t>G_Olsenella</t>
+  </si>
+  <si>
+    <t>G_Devosia</t>
+  </si>
+  <si>
+    <t>G_Haemophilus</t>
+  </si>
+  <si>
+    <t>G_Rubellimicrobium</t>
+  </si>
+  <si>
+    <t>G_Cloacibacillus</t>
+  </si>
+  <si>
+    <t>G_Paludibacter</t>
+  </si>
+  <si>
+    <t>G_Capnocytophaga</t>
+  </si>
+  <si>
+    <t>G_Adlercreutzia</t>
+  </si>
+  <si>
+    <t>G_Thermobacillus</t>
+  </si>
+  <si>
+    <t>G_Barnesiella</t>
+  </si>
+  <si>
+    <t>G_Peredibacter</t>
+  </si>
+  <si>
+    <t>G_Methylibium</t>
+  </si>
+  <si>
+    <t>G_Bordetella</t>
+  </si>
+  <si>
+    <t>F_Rhodobacteraceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Enterorhabdus</t>
+  </si>
+  <si>
+    <t>G_Papillibacter</t>
+  </si>
+  <si>
+    <t>G_Varibaculum</t>
+  </si>
+  <si>
+    <t>G_Bilophila</t>
+  </si>
+  <si>
+    <t>G_Cloacibacterium</t>
+  </si>
+  <si>
+    <t>G_Sphingobacterium</t>
+  </si>
+  <si>
+    <t>G_Chryseobacterium</t>
+  </si>
+  <si>
+    <t>G_Rhizobium</t>
+  </si>
+  <si>
+    <t>G_Achromobacter</t>
+  </si>
+  <si>
+    <t>G_Brevundimonas</t>
+  </si>
+  <si>
+    <t>G_Bdellovibrio</t>
+  </si>
+  <si>
+    <t>G_Paraprevotella</t>
+  </si>
+  <si>
+    <t>G_Roseomonas</t>
+  </si>
+  <si>
+    <t>G_Oscillibacter</t>
+  </si>
+  <si>
+    <t>G_Candidimonas</t>
+  </si>
+  <si>
+    <t>G_Azohydromonas</t>
+  </si>
+  <si>
+    <t>G_Lachnoanaerobaculum</t>
+  </si>
+  <si>
+    <t>G_Zoogloea</t>
+  </si>
+  <si>
+    <t>G_Lysobacter</t>
+  </si>
+  <si>
+    <t>F_Cytophagaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Pannonibacter</t>
+  </si>
+  <si>
+    <t>G_Paenibacillus</t>
+  </si>
+  <si>
+    <t>F_Sandaracinaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Sporosarcina</t>
+  </si>
+  <si>
+    <t>F_Prevotellaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Pseudoalteromonas</t>
+  </si>
+  <si>
+    <t>G_Porphyromonas</t>
+  </si>
+  <si>
+    <t>G_Rhodoligotrophos</t>
+  </si>
+  <si>
+    <t>F_Phycisphaeraceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Anaerofilum</t>
+  </si>
+  <si>
+    <t>G_Hirschia</t>
+  </si>
+  <si>
+    <t>G_Altererythrobacter</t>
+  </si>
+  <si>
+    <t>G_Alloprevotella</t>
+  </si>
+  <si>
+    <t>G_Simiduia</t>
+  </si>
+  <si>
+    <t>G_Haloplasma</t>
+  </si>
+  <si>
+    <t>F_Anaerolineaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Pedomicrobium</t>
+  </si>
+  <si>
+    <t>G_Truepera</t>
+  </si>
+  <si>
+    <t>G_Patulibacter</t>
+  </si>
+  <si>
+    <t>G_Aquicella</t>
+  </si>
+  <si>
+    <t>G_Oxalobacter</t>
+  </si>
+  <si>
+    <t>F_Hyphomonadaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Alloiococcus</t>
+  </si>
+  <si>
+    <t>F_Sphingomonadaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Caldilineaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Rickettsiaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Eubacterium</t>
+  </si>
+  <si>
+    <t>G_Aquincola</t>
+  </si>
+  <si>
+    <t>G_Anaerotruncus</t>
+  </si>
+  <si>
+    <t>G_Pseudospirillum</t>
+  </si>
+  <si>
+    <t>G_Thermomonas</t>
+  </si>
+  <si>
+    <t>G_Deinococcus</t>
+  </si>
+  <si>
+    <t>G_Pedobacter</t>
+  </si>
+  <si>
+    <t>G_Alcanivorax</t>
+  </si>
+  <si>
+    <t>G_Intestinimonas</t>
+  </si>
+  <si>
+    <t>F_Acidimicrobiaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Thermoactinomycetaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>F_Peptococcaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Parasutterella</t>
+  </si>
+  <si>
+    <t>F_Xanthomonadaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Tatumella</t>
+  </si>
+  <si>
+    <t>G_Rheinheimera</t>
+  </si>
+  <si>
+    <t>G_Neisseria</t>
+  </si>
+  <si>
+    <t>F_Peptostreptococcaceae_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Herbaspirillum_huttiense</t>
+  </si>
+  <si>
+    <t>G_Bifidobacterium_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Bacillus_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Enterococcus_durans</t>
+  </si>
+  <si>
+    <t>G_Ruminococcus_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Parabacteroides_distasonis</t>
+  </si>
+  <si>
+    <t>G_Lactobacillus_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Lachnospira_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Catenibacterium_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Pseudomonas_azotoformans</t>
+  </si>
+  <si>
+    <t>S_Sphingomonas_paucimobilis</t>
+  </si>
+  <si>
+    <t>S_Undibacterium_pigrum</t>
+  </si>
+  <si>
+    <t>G_Roseburia_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Subdoligranulum_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Staphylococcus_sciuri</t>
+  </si>
+  <si>
+    <t>G_Sphingomonas_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Acinetobacter_guillouiae</t>
+  </si>
+  <si>
+    <t>S_Bacteroides_uniformis</t>
+  </si>
+  <si>
+    <t>G_Curvibacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Streptococcus_parasanguinis</t>
+  </si>
+  <si>
+    <t>G_Stenotrophomonas_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Anaerosporobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Bacteroides_vulgatus_ATCC_8482</t>
+  </si>
+  <si>
+    <t>S_Streptococcus_pyogenes</t>
+  </si>
+  <si>
+    <t>G_Dorea_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Alistipes_onderdonkii_DSM_19147</t>
+  </si>
+  <si>
+    <t>S_Eubacterium_rectale_ATCC_33656</t>
+  </si>
+  <si>
+    <t>G_Sutterella_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Pelomonas_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Bacteroides_thetaiotaomicron</t>
+  </si>
+  <si>
+    <t>G_Veillonella_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Methylophilus_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Megasphaera_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Bacteroides_ovatus</t>
+  </si>
+  <si>
+    <t>S_Burkholderia_caledonica</t>
+  </si>
+  <si>
+    <t>G_Anaerostipes_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Acinetobacter_calcoaceticus</t>
+  </si>
+  <si>
+    <t>S_Ralstonia_pickettii</t>
+  </si>
+  <si>
+    <t>S_Desulfovibrio_piger</t>
+  </si>
+  <si>
+    <t>G_Bacteroides_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Ochrobactrum_intermedium</t>
+  </si>
+  <si>
+    <t>S_Ruminococcus_sp._80/3</t>
+  </si>
+  <si>
+    <t>S_Serratia_marcescens</t>
+  </si>
+  <si>
+    <t>G_Planifilum_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Parapedobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Staphylococcus_capitis</t>
+  </si>
+  <si>
+    <t>S_unidentified</t>
+  </si>
+  <si>
+    <t>S_Prevotella_sp._DJF_LS16</t>
+  </si>
+  <si>
+    <t>S_Mesorhizobium_amorphae</t>
+  </si>
+  <si>
+    <t>S_Bacteroides_caccae</t>
+  </si>
+  <si>
+    <t>G_Tabrizicola_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Actinomyces_odontolyticus</t>
+  </si>
+  <si>
+    <t>G_Prevotella_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Parabacteroides_merdae</t>
+  </si>
+  <si>
+    <t>S_Megasphaera_elsdenii</t>
+  </si>
+  <si>
+    <t>S_Ruminococcus_sp._5_1_39BFAA</t>
+  </si>
+  <si>
+    <t>S_butyrate-producing_bacterium_L2-50</t>
+  </si>
+  <si>
+    <t>G_Blautia_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Sphaerobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Lysinibacillus_massiliensis</t>
+  </si>
+  <si>
+    <t>S_Providencia_rettgeri</t>
+  </si>
+  <si>
+    <t>S_Bacteroides_massiliensis</t>
+  </si>
+  <si>
+    <t>S_Slackia_piriformis</t>
+  </si>
+  <si>
+    <t>S_Fusobacterium_nucleatum</t>
+  </si>
+  <si>
+    <t>G_Butyricimonas_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Allobaculum_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Parabacteroides_goldsteinii</t>
+  </si>
+  <si>
+    <t>G_Flavobacterium_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Lactobacillus_fermentum</t>
+  </si>
+  <si>
+    <t>G_Sulfuritalea_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Pseudoxanthomonas_mexicana</t>
+  </si>
+  <si>
+    <t>G_Mitsuokella_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Actinomyces_graevenitzii</t>
+  </si>
+  <si>
+    <t>S_human_gut_metagenome</t>
+  </si>
+  <si>
+    <t>G_Hydrogenophaga_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Streptococcus_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Phascolarctobacterium_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Dolosigranulum_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Dialister_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Leptotrichia_hofstadii</t>
+  </si>
+  <si>
+    <t>S_Lactobacillus_intestinalis</t>
+  </si>
+  <si>
+    <t>S_Fusobacterium_varium</t>
+  </si>
+  <si>
+    <t>S_Prevotella_buccae</t>
+  </si>
+  <si>
+    <t>G_Parabacteroides_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Alistipes_indistinctus_YIT_12060</t>
+  </si>
+  <si>
+    <t>G_Coprobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Acidaminococcus_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Olsenella_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Devosia_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Haemophilus_parainfluenzae</t>
+  </si>
+  <si>
+    <t>G_Rubellimicrobium_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Cloacibacillus_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Bacteroidetes_oral_taxon_274_str._F0058</t>
+  </si>
+  <si>
+    <t>G_Capnocytophaga_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Adlercreutzia_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Thermobacillus_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Barnesiella_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Peredibacter_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Methylibium_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Bordetella_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Enterorhabdus_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Lactobacillus_casei</t>
+  </si>
+  <si>
+    <t>G_Coprococcus_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Papillibacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Varibaculum_cambriense</t>
+  </si>
+  <si>
+    <t>S_Streptococcus_anginosus</t>
+  </si>
+  <si>
+    <t>S_Bilophila_wadsworthia</t>
+  </si>
+  <si>
+    <t>G_Cloacibacterium_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Haemophilus_influenzae</t>
+  </si>
+  <si>
+    <t>G_Desulfovibrio_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Sphingobacterium_multivorum</t>
+  </si>
+  <si>
+    <t>G_Chryseobacterium_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Bacteroides_plebeius</t>
+  </si>
+  <si>
+    <t>S_Rhizobium_sp._CC-LY845</t>
+  </si>
+  <si>
+    <t>G_Achromobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Streptococcus_salivarius</t>
+  </si>
+  <si>
+    <t>S_Brevundimonas_diminuta</t>
+  </si>
+  <si>
+    <t>G_Bdellovibrio_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Paraprevotella_xylaniphila</t>
+  </si>
+  <si>
+    <t>S_Roseomonas_mucosa</t>
+  </si>
+  <si>
+    <t>S_Oscillibacter_ruminantium_GH1</t>
+  </si>
+  <si>
+    <t>S_Achromobacter_sp._MTCC_11931</t>
+  </si>
+  <si>
+    <t>G_Actinomyces_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Azohydromonas_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Lachnoanaerobaculum_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Zoogloea_resiniphila</t>
+  </si>
+  <si>
+    <t>G_Lysobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Bacillus_beringensis</t>
+  </si>
+  <si>
+    <t>G_Pannonibacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Paenibacillus_timonensis</t>
+  </si>
+  <si>
+    <t>S_Desulfovibrio_simplex</t>
+  </si>
+  <si>
+    <t>G_Sporosarcina_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Leptotrichia_sp._oral_clone_IK040</t>
+  </si>
+  <si>
+    <t>S_Flavobacterium_ummariense</t>
+  </si>
+  <si>
+    <t>G_Pseudoalteromonas_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Porphyromonas_Unclassified</t>
+  </si>
+  <si>
+    <t>S_alpha_proteobacterium_S22-37</t>
+  </si>
+  <si>
+    <t>G_Anaerofilum_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Hirschia_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Altererythrobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Lactobacillus_agilis</t>
+  </si>
+  <si>
+    <t>S_Alloprevotella_tannerae</t>
+  </si>
+  <si>
+    <t>G_Simiduia_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Haloplasma_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Pedomicrobium_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Truepera_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Patulibacter_minatonensis</t>
+  </si>
+  <si>
+    <t>G_Aquicella_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Oxalobacter_formigenes</t>
+  </si>
+  <si>
+    <t>G_Alloiococcus_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Paenibacillus_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Flavobacterium_cucumis</t>
+  </si>
+  <si>
+    <t>S_Prevotella_nigrescens</t>
+  </si>
+  <si>
+    <t>G_Eubacterium_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Aquincola_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Anaerotruncus_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Lactobacillus_paralimentarius</t>
+  </si>
+  <si>
+    <t>G_Pseudospirillum_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Thermomonas_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Deinococcus_grandis</t>
+  </si>
+  <si>
+    <t>S_Pedobacter_heparinus_DSM_2366</t>
+  </si>
+  <si>
+    <t>G_Alcanivorax_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Roseomonas_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Thermobacillus_composti_KWC4</t>
+  </si>
+  <si>
+    <t>G_Intestinimonas_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Sutterella_parvirubra</t>
+  </si>
+  <si>
+    <t>S_Flavobacterium_marinum</t>
+  </si>
+  <si>
+    <t>G_Alloprevotella_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Parasutterella_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Rosenbergiella_nectarea</t>
+  </si>
+  <si>
+    <t>G_Rheinheimera_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Neisseria_Unclassified</t>
+  </si>
+  <si>
+    <t>G_Acinetobacter_Unclassified</t>
+  </si>
+  <si>
+    <t>S_Phascolarctobacterium_faecium</t>
+  </si>
+  <si>
+    <t>S_Blautia_producta</t>
   </si>
 </sst>
 </file>
@@ -2445,10 +2577,10 @@
         <v>401</v>
       </c>
       <c r="D2" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="3">
@@ -2462,10 +2594,10 @@
         <v>402</v>
       </c>
       <c r="D3" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E3" t="s">
-        <v>412</v>
+        <v>656</v>
       </c>
     </row>
     <row r="4">
@@ -2479,10 +2611,10 @@
         <v>403</v>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E4" t="s">
-        <v>412</v>
+        <v>657</v>
       </c>
     </row>
     <row r="5">
@@ -2496,10 +2628,10 @@
         <v>404</v>
       </c>
       <c r="D5" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E5" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6">
@@ -2513,10 +2645,10 @@
         <v>405</v>
       </c>
       <c r="D6" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E6" t="s">
-        <v>412</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7">
@@ -2530,10 +2662,10 @@
         <v>406</v>
       </c>
       <c r="D7" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E7" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -2547,10 +2679,10 @@
         <v>407</v>
       </c>
       <c r="D8" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E8" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9">
@@ -2564,10 +2696,10 @@
         <v>408</v>
       </c>
       <c r="D9" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E9" t="s">
-        <v>412</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10">
@@ -2581,10 +2713,10 @@
         <v>407</v>
       </c>
       <c r="D10" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="E10" t="s">
-        <v>412</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11">
@@ -2598,10 +2730,10 @@
         <v>409</v>
       </c>
       <c r="D11" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="E11" t="s">
-        <v>412</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12">
@@ -2615,10 +2747,10 @@
         <v>410</v>
       </c>
       <c r="D12" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="E12" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13">
@@ -2632,10 +2764,10 @@
         <v>411</v>
       </c>
       <c r="D13" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="E13" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14">
@@ -2649,10 +2781,10 @@
         <v>405</v>
       </c>
       <c r="D14" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E14" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15">
@@ -2666,10 +2798,10 @@
         <v>401</v>
       </c>
       <c r="D15" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="E15" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
     </row>
     <row r="16">
@@ -2700,10 +2832,10 @@
         <v>407</v>
       </c>
       <c r="D17" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="E17" t="s">
-        <v>412</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18">
@@ -2717,10 +2849,10 @@
         <v>405</v>
       </c>
       <c r="D18" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="E18" t="s">
-        <v>412</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19">
@@ -2734,10 +2866,10 @@
         <v>413</v>
       </c>
       <c r="D19" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="E19" t="s">
-        <v>656</v>
+        <v>669</v>
       </c>
     </row>
     <row r="20">
@@ -2751,10 +2883,10 @@
         <v>411</v>
       </c>
       <c r="D20" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="E20" t="s">
-        <v>412</v>
+        <v>670</v>
       </c>
     </row>
     <row r="21">
@@ -2768,10 +2900,10 @@
         <v>414</v>
       </c>
       <c r="D21" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="E21" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22">
@@ -2785,10 +2917,10 @@
         <v>409</v>
       </c>
       <c r="D22" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="E22" t="s">
-        <v>658</v>
+        <v>521</v>
       </c>
     </row>
     <row r="23">
@@ -2802,10 +2934,10 @@
         <v>415</v>
       </c>
       <c r="D23" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E23" t="s">
-        <v>659</v>
+        <v>672</v>
       </c>
     </row>
     <row r="24">
@@ -2819,10 +2951,10 @@
         <v>416</v>
       </c>
       <c r="D24" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="E24" t="s">
-        <v>412</v>
+        <v>673</v>
       </c>
     </row>
     <row r="25">
@@ -2836,10 +2968,10 @@
         <v>417</v>
       </c>
       <c r="D25" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="E25" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
     </row>
     <row r="26">
@@ -2853,10 +2985,10 @@
         <v>418</v>
       </c>
       <c r="D26" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="E26" t="s">
-        <v>412</v>
+        <v>675</v>
       </c>
     </row>
     <row r="27">
@@ -2870,10 +3002,10 @@
         <v>407</v>
       </c>
       <c r="D27" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="E27" t="s">
-        <v>412</v>
+        <v>676</v>
       </c>
     </row>
     <row r="28">
@@ -2887,10 +3019,10 @@
         <v>415</v>
       </c>
       <c r="D28" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E28" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29">
@@ -2904,10 +3036,10 @@
         <v>417</v>
       </c>
       <c r="D29" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="E29" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
     </row>
     <row r="30">
@@ -2921,10 +3053,10 @@
         <v>407</v>
       </c>
       <c r="D30" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E30" t="s">
-        <v>412</v>
+        <v>679</v>
       </c>
     </row>
     <row r="31">
@@ -2938,10 +3070,10 @@
         <v>419</v>
       </c>
       <c r="D31" t="s">
-        <v>422</v>
+        <v>528</v>
       </c>
       <c r="E31" t="s">
-        <v>663</v>
+        <v>528</v>
       </c>
     </row>
     <row r="32">
@@ -2955,10 +3087,10 @@
         <v>420</v>
       </c>
       <c r="D32" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E32" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33">
@@ -2972,10 +3104,10 @@
         <v>405</v>
       </c>
       <c r="D33" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E33" t="s">
-        <v>665</v>
+        <v>515</v>
       </c>
     </row>
     <row r="34">
@@ -2989,10 +3121,10 @@
         <v>407</v>
       </c>
       <c r="D34" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="E34" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
     </row>
     <row r="35">
@@ -3006,10 +3138,10 @@
         <v>421</v>
       </c>
       <c r="D35" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E35" t="s">
-        <v>412</v>
+        <v>682</v>
       </c>
     </row>
     <row r="36">
@@ -3023,10 +3155,10 @@
         <v>407</v>
       </c>
       <c r="D36" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="E36" t="s">
-        <v>412</v>
+        <v>662</v>
       </c>
     </row>
     <row r="37">
@@ -3037,13 +3169,13 @@
         <v>0.36663022610369134</v>
       </c>
       <c r="C37" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D37" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E37" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="38">
@@ -3057,10 +3189,10 @@
         <v>416</v>
       </c>
       <c r="D38" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="E38" t="s">
-        <v>412</v>
+        <v>683</v>
       </c>
     </row>
     <row r="39">
@@ -3074,10 +3206,10 @@
         <v>415</v>
       </c>
       <c r="D39" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E39" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
     </row>
     <row r="40">
@@ -3091,10 +3223,10 @@
         <v>407</v>
       </c>
       <c r="D40" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E40" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="41">
@@ -3105,13 +3237,13 @@
         <v>0.31534196483561355</v>
       </c>
       <c r="C41" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D41" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E41" t="s">
-        <v>668</v>
+        <v>423</v>
       </c>
     </row>
     <row r="42">
@@ -3122,13 +3254,13 @@
         <v>0.3110312807645645</v>
       </c>
       <c r="C42" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D42" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E42" t="s">
-        <v>412</v>
+        <v>685</v>
       </c>
     </row>
     <row r="43">
@@ -3142,10 +3274,10 @@
         <v>407</v>
       </c>
       <c r="D43" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E43" t="s">
-        <v>665</v>
+        <v>509</v>
       </c>
     </row>
     <row r="44">
@@ -3156,13 +3288,13 @@
         <v>0.3066001535647785</v>
       </c>
       <c r="C44" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D44" t="s">
-        <v>522</v>
+        <v>425</v>
       </c>
       <c r="E44" t="s">
-        <v>669</v>
+        <v>425</v>
       </c>
     </row>
     <row r="45">
@@ -3173,13 +3305,13 @@
         <v>0.303547890479426</v>
       </c>
       <c r="C45" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D45" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E45" t="s">
-        <v>670</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46">
@@ -3190,13 +3322,13 @@
         <v>0.3022952178180965</v>
       </c>
       <c r="C46" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D46" t="s">
-        <v>412</v>
+        <v>534</v>
       </c>
       <c r="E46" t="s">
-        <v>412</v>
+        <v>534</v>
       </c>
     </row>
     <row r="47">
@@ -3207,13 +3339,13 @@
         <v>0.29550063481732003</v>
       </c>
       <c r="C47" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D47" t="s">
-        <v>523</v>
+        <v>425</v>
       </c>
       <c r="E47" t="s">
-        <v>671</v>
+        <v>425</v>
       </c>
     </row>
     <row r="48">
@@ -3227,10 +3359,10 @@
         <v>419</v>
       </c>
       <c r="D48" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="E48" t="s">
-        <v>412</v>
+        <v>686</v>
       </c>
     </row>
     <row r="49">
@@ -3241,13 +3373,13 @@
         <v>0.2853438192528894</v>
       </c>
       <c r="C49" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="D49" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="E49" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
     </row>
     <row r="50">
@@ -3258,13 +3390,13 @@
         <v>0.28207293822326995</v>
       </c>
       <c r="C50" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D50" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="E50" t="s">
-        <v>412</v>
+        <v>687</v>
       </c>
     </row>
     <row r="51">
@@ -3278,10 +3410,10 @@
         <v>415</v>
       </c>
       <c r="D51" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E51" t="s">
-        <v>672</v>
+        <v>688</v>
       </c>
     </row>
     <row r="52">
@@ -3295,10 +3427,10 @@
         <v>405</v>
       </c>
       <c r="D52" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E52" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="53">
@@ -3309,13 +3441,13 @@
         <v>0.2720655781621473</v>
       </c>
       <c r="C53" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D53" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="E53" t="s">
-        <v>673</v>
+        <v>689</v>
       </c>
     </row>
     <row r="54">
@@ -3329,10 +3461,10 @@
         <v>407</v>
       </c>
       <c r="D54" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="E54" t="s">
-        <v>412</v>
+        <v>690</v>
       </c>
     </row>
     <row r="55">
@@ -3346,10 +3478,10 @@
         <v>414</v>
       </c>
       <c r="D55" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="E55" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
     </row>
     <row r="56">
@@ -3360,13 +3492,13 @@
         <v>0.2666088257564815</v>
       </c>
       <c r="C56" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D56" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="E56" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
     </row>
     <row r="57">
@@ -3377,13 +3509,13 @@
         <v>0.2663920798008212</v>
       </c>
       <c r="C57" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D57" t="s">
-        <v>529</v>
+        <v>425</v>
       </c>
       <c r="E57" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="58">
@@ -3394,13 +3526,13 @@
         <v>0.2645647048384008</v>
       </c>
       <c r="C58" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D58" t="s">
-        <v>412</v>
+        <v>540</v>
       </c>
       <c r="E58" t="s">
-        <v>412</v>
+        <v>540</v>
       </c>
     </row>
     <row r="59">
@@ -3411,13 +3543,13 @@
         <v>0.25953845121518343</v>
       </c>
       <c r="C59" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D59" t="s">
-        <v>412</v>
+        <v>541</v>
       </c>
       <c r="E59" t="s">
-        <v>412</v>
+        <v>541</v>
       </c>
     </row>
     <row r="60">
@@ -3428,13 +3560,13 @@
         <v>0.25836339887956977</v>
       </c>
       <c r="C60" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D60" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E60" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
     </row>
     <row r="61">
@@ -3448,10 +3580,10 @@
         <v>415</v>
       </c>
       <c r="D61" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E61" t="s">
-        <v>412</v>
+        <v>694</v>
       </c>
     </row>
     <row r="62">
@@ -3462,13 +3594,13 @@
         <v>0.25430511209776724</v>
       </c>
       <c r="C62" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D62" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="E62" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
     </row>
     <row r="63">
@@ -3482,10 +3614,10 @@
         <v>407</v>
       </c>
       <c r="D63" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E63" t="s">
-        <v>678</v>
+        <v>509</v>
       </c>
     </row>
     <row r="64">
@@ -3499,10 +3631,10 @@
         <v>405</v>
       </c>
       <c r="D64" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E64" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
     </row>
     <row r="65">
@@ -3513,13 +3645,13 @@
         <v>0.24495586195806365</v>
       </c>
       <c r="C65" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="D65" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="E65" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
     </row>
     <row r="66">
@@ -3530,13 +3662,13 @@
         <v>0.2442438818377673</v>
       </c>
       <c r="C66" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D66" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E66" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
     </row>
     <row r="67">
@@ -3547,13 +3679,13 @@
         <v>0.24119643982193503</v>
       </c>
       <c r="C67" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D67" t="s">
-        <v>533</v>
+        <v>425</v>
       </c>
       <c r="E67" t="s">
-        <v>681</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68">
@@ -3564,13 +3696,13 @@
         <v>0.2405220264312716</v>
       </c>
       <c r="C68" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D68" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="E68" t="s">
-        <v>412</v>
+        <v>698</v>
       </c>
     </row>
     <row r="69">
@@ -3581,13 +3713,13 @@
         <v>0.23823815018048555</v>
       </c>
       <c r="C69" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="D69" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="E69" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
     </row>
     <row r="70">
@@ -3598,13 +3730,13 @@
         <v>0.233943382875701</v>
       </c>
       <c r="C70" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D70" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E70" t="s">
-        <v>412</v>
+        <v>699</v>
       </c>
     </row>
     <row r="71">
@@ -3615,13 +3747,13 @@
         <v>0.23326131655869523</v>
       </c>
       <c r="C71" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="D71" t="s">
-        <v>536</v>
+        <v>425</v>
       </c>
       <c r="E71" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="72">
@@ -3635,10 +3767,10 @@
         <v>407</v>
       </c>
       <c r="D72" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E72" t="s">
-        <v>663</v>
+        <v>509</v>
       </c>
     </row>
     <row r="73">
@@ -3652,10 +3784,10 @@
         <v>405</v>
       </c>
       <c r="D73" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E73" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="74">
@@ -3669,10 +3801,10 @@
         <v>405</v>
       </c>
       <c r="D74" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E74" t="s">
-        <v>682</v>
+        <v>515</v>
       </c>
     </row>
     <row r="75">
@@ -3686,10 +3818,10 @@
         <v>413</v>
       </c>
       <c r="D75" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="E75" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
     </row>
     <row r="76">
@@ -3703,10 +3835,10 @@
         <v>407</v>
       </c>
       <c r="D76" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E76" t="s">
-        <v>663</v>
+        <v>701</v>
       </c>
     </row>
     <row r="77">
@@ -3720,10 +3852,10 @@
         <v>407</v>
       </c>
       <c r="D77" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E77" t="s">
-        <v>684</v>
+        <v>509</v>
       </c>
     </row>
     <row r="78">
@@ -3737,10 +3869,10 @@
         <v>405</v>
       </c>
       <c r="D78" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E78" t="s">
-        <v>685</v>
+        <v>515</v>
       </c>
     </row>
     <row r="79">
@@ -3751,13 +3883,13 @@
         <v>0.2276055966001193</v>
       </c>
       <c r="C79" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D79" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="E79" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
     </row>
     <row r="80">
@@ -3768,13 +3900,13 @@
         <v>0.2272606806073618</v>
       </c>
       <c r="C80" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D80" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="E80" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
     </row>
     <row r="81">
@@ -3785,13 +3917,13 @@
         <v>0.22477942019646235</v>
       </c>
       <c r="C81" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D81" t="s">
-        <v>533</v>
+        <v>425</v>
       </c>
       <c r="E81" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="82">
@@ -3802,13 +3934,13 @@
         <v>0.2239718187454051</v>
       </c>
       <c r="C82" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D82" t="s">
-        <v>422</v>
+        <v>550</v>
       </c>
       <c r="E82" t="s">
-        <v>688</v>
+        <v>550</v>
       </c>
     </row>
     <row r="83">
@@ -3819,13 +3951,13 @@
         <v>0.22151368293829068</v>
       </c>
       <c r="C83" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D83" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E83" t="s">
-        <v>689</v>
+        <v>423</v>
       </c>
     </row>
     <row r="84">
@@ -3839,10 +3971,10 @@
         <v>415</v>
       </c>
       <c r="D84" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E84" t="s">
-        <v>690</v>
+        <v>704</v>
       </c>
     </row>
     <row r="85">
@@ -3856,10 +3988,10 @@
         <v>405</v>
       </c>
       <c r="D85" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E85" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="86">
@@ -3870,13 +4002,13 @@
         <v>0.21936211219230206</v>
       </c>
       <c r="C86" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D86" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="E86" t="s">
-        <v>412</v>
+        <v>705</v>
       </c>
     </row>
     <row r="87">
@@ -3890,10 +4022,10 @@
         <v>405</v>
       </c>
       <c r="D87" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E87" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="88">
@@ -3907,10 +4039,10 @@
         <v>407</v>
       </c>
       <c r="D88" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E88" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="89">
@@ -3921,13 +4053,13 @@
         <v>0.21484962654050183</v>
       </c>
       <c r="C89" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D89" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E89" t="s">
-        <v>691</v>
+        <v>706</v>
       </c>
     </row>
     <row r="90">
@@ -3938,13 +4070,13 @@
         <v>0.21387356566577104</v>
       </c>
       <c r="C90" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D90" t="s">
-        <v>412</v>
+        <v>553</v>
       </c>
       <c r="E90" t="s">
-        <v>412</v>
+        <v>553</v>
       </c>
     </row>
     <row r="91">
@@ -3955,13 +4087,13 @@
         <v>0.21363534297590675</v>
       </c>
       <c r="C91" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D91" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="E91" t="s">
-        <v>412</v>
+        <v>707</v>
       </c>
     </row>
     <row r="92">
@@ -3975,10 +4107,10 @@
         <v>406</v>
       </c>
       <c r="D92" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E92" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
     </row>
     <row r="93">
@@ -3989,13 +4121,13 @@
         <v>0.2125619952935362</v>
       </c>
       <c r="C93" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="D93" t="s">
-        <v>542</v>
+        <v>425</v>
       </c>
       <c r="E93" t="s">
-        <v>693</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94">
@@ -4006,13 +4138,13 @@
         <v>0.21207008726291574</v>
       </c>
       <c r="C94" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D94" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="E94" t="s">
-        <v>694</v>
+        <v>709</v>
       </c>
     </row>
     <row r="95">
@@ -4026,10 +4158,10 @@
         <v>405</v>
       </c>
       <c r="D95" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E95" t="s">
-        <v>695</v>
+        <v>515</v>
       </c>
     </row>
     <row r="96">
@@ -4040,13 +4172,13 @@
         <v>0.21197105989027012</v>
       </c>
       <c r="C96" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="D96" t="s">
-        <v>543</v>
+        <v>425</v>
       </c>
       <c r="E96" t="s">
-        <v>696</v>
+        <v>425</v>
       </c>
     </row>
     <row r="97">
@@ -4057,13 +4189,13 @@
         <v>0.21131302854400377</v>
       </c>
       <c r="C97" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D97" t="s">
-        <v>412</v>
+        <v>554</v>
       </c>
       <c r="E97" t="s">
-        <v>412</v>
+        <v>554</v>
       </c>
     </row>
     <row r="98">
@@ -4077,10 +4209,10 @@
         <v>407</v>
       </c>
       <c r="D98" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E98" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
     </row>
     <row r="99">
@@ -4094,10 +4226,10 @@
         <v>407</v>
       </c>
       <c r="D99" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="E99" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="100">
@@ -4108,13 +4240,13 @@
         <v>0.20976488411887512</v>
       </c>
       <c r="C100" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D100" t="s">
-        <v>545</v>
+        <v>423</v>
       </c>
       <c r="E100" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="101">
@@ -4128,10 +4260,10 @@
         <v>407</v>
       </c>
       <c r="D101" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E101" t="s">
-        <v>412</v>
+        <v>712</v>
       </c>
     </row>
     <row r="102">
@@ -4142,13 +4274,13 @@
         <v>0.20802629606741144</v>
       </c>
       <c r="C102" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D102" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="E102" t="s">
-        <v>412</v>
+        <v>713</v>
       </c>
     </row>
     <row r="103">
@@ -4162,10 +4294,10 @@
         <v>407</v>
       </c>
       <c r="D103" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E103" t="s">
-        <v>699</v>
+        <v>509</v>
       </c>
     </row>
     <row r="104">
@@ -4176,13 +4308,13 @@
         <v>0.2080205403002394</v>
       </c>
       <c r="C104" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D104" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="E104" t="s">
-        <v>700</v>
+        <v>714</v>
       </c>
     </row>
     <row r="105">
@@ -4193,13 +4325,13 @@
         <v>0.20717446429077252</v>
       </c>
       <c r="C105" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="D105" t="s">
-        <v>548</v>
+        <v>425</v>
       </c>
       <c r="E105" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="106">
@@ -4210,13 +4342,13 @@
         <v>0.20603668844275194</v>
       </c>
       <c r="C106" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D106" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="E106" t="s">
-        <v>701</v>
+        <v>715</v>
       </c>
     </row>
     <row r="107">
@@ -4230,10 +4362,10 @@
         <v>415</v>
       </c>
       <c r="D107" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E107" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
     </row>
     <row r="108">
@@ -4244,13 +4376,13 @@
         <v>0.20468136089908726</v>
       </c>
       <c r="C108" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D108" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="E108" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
     </row>
     <row r="109">
@@ -4261,13 +4393,13 @@
         <v>0.20446896854617455</v>
       </c>
       <c r="C109" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="D109" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="E109" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="110">
@@ -4278,13 +4410,13 @@
         <v>0.20300936590910468</v>
       </c>
       <c r="C110" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D110" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="E110" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
     </row>
     <row r="111">
@@ -4295,13 +4427,13 @@
         <v>0.20226824585300857</v>
       </c>
       <c r="C111" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="D111" t="s">
-        <v>552</v>
+        <v>425</v>
       </c>
       <c r="E111" t="s">
-        <v>705</v>
+        <v>425</v>
       </c>
     </row>
     <row r="112">
@@ -4315,10 +4447,10 @@
         <v>406</v>
       </c>
       <c r="D112" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="E112" t="s">
-        <v>412</v>
+        <v>719</v>
       </c>
     </row>
     <row r="113">
@@ -4329,13 +4461,13 @@
         <v>0.20067609021650148</v>
       </c>
       <c r="C113" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="D113" t="s">
-        <v>554</v>
+        <v>425</v>
       </c>
       <c r="E113" t="s">
-        <v>706</v>
+        <v>425</v>
       </c>
     </row>
     <row r="114">
@@ -4349,10 +4481,10 @@
         <v>409</v>
       </c>
       <c r="D114" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="E114" t="s">
-        <v>412</v>
+        <v>720</v>
       </c>
     </row>
     <row r="115">
@@ -4366,10 +4498,10 @@
         <v>406</v>
       </c>
       <c r="D115" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E115" t="s">
-        <v>707</v>
+        <v>721</v>
       </c>
     </row>
     <row r="116">
@@ -4380,13 +4512,13 @@
         <v>0.1992636694100667</v>
       </c>
       <c r="C116" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D116" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E116" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="117">
@@ -4397,13 +4529,13 @@
         <v>0.1988955641556601</v>
       </c>
       <c r="C117" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="D117" t="s">
-        <v>556</v>
+        <v>425</v>
       </c>
       <c r="E117" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="118">
@@ -4417,10 +4549,10 @@
         <v>407</v>
       </c>
       <c r="D118" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E118" t="s">
-        <v>708</v>
+        <v>509</v>
       </c>
     </row>
     <row r="119">
@@ -4434,10 +4566,10 @@
         <v>407</v>
       </c>
       <c r="D119" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E119" t="s">
-        <v>709</v>
+        <v>509</v>
       </c>
     </row>
     <row r="120">
@@ -4448,13 +4580,13 @@
         <v>0.19615558009990933</v>
       </c>
       <c r="C120" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D120" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E120" t="s">
-        <v>412</v>
+        <v>722</v>
       </c>
     </row>
     <row r="121">
@@ -4465,13 +4597,13 @@
         <v>0.19518080517848665</v>
       </c>
       <c r="C121" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D121" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
       <c r="E121" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
     </row>
     <row r="122">
@@ -4485,10 +4617,10 @@
         <v>408</v>
       </c>
       <c r="D122" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E122" t="s">
-        <v>710</v>
+        <v>723</v>
       </c>
     </row>
     <row r="123">
@@ -4499,13 +4631,13 @@
         <v>0.193975653368999</v>
       </c>
       <c r="C123" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D123" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E123" t="s">
-        <v>711</v>
+        <v>426</v>
       </c>
     </row>
     <row r="124">
@@ -4516,13 +4648,13 @@
         <v>0.1937213515255721</v>
       </c>
       <c r="C124" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D124" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="E124" t="s">
-        <v>412</v>
+        <v>724</v>
       </c>
     </row>
     <row r="125">
@@ -4536,10 +4668,10 @@
         <v>407</v>
       </c>
       <c r="D125" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="E125" t="s">
-        <v>412</v>
+        <v>667</v>
       </c>
     </row>
     <row r="126">
@@ -4553,10 +4685,10 @@
         <v>418</v>
       </c>
       <c r="D126" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="E126" t="s">
-        <v>712</v>
+        <v>725</v>
       </c>
     </row>
     <row r="127">
@@ -4567,13 +4699,13 @@
         <v>0.1918793741964194</v>
       </c>
       <c r="C127" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D127" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="E127" t="s">
-        <v>412</v>
+        <v>726</v>
       </c>
     </row>
     <row r="128">
@@ -4584,13 +4716,13 @@
         <v>0.19061040533546258</v>
       </c>
       <c r="C128" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D128" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E128" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
     </row>
     <row r="129">
@@ -4604,10 +4736,10 @@
         <v>405</v>
       </c>
       <c r="D129" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E129" t="s">
-        <v>665</v>
+        <v>728</v>
       </c>
     </row>
     <row r="130">
@@ -4618,13 +4750,13 @@
         <v>0.18999536651401025</v>
       </c>
       <c r="C130" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="D130" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="E130" t="s">
-        <v>714</v>
+        <v>452</v>
       </c>
     </row>
     <row r="131">
@@ -4635,13 +4767,13 @@
         <v>0.188585719684493</v>
       </c>
       <c r="C131" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D131" t="s">
-        <v>412</v>
+        <v>534</v>
       </c>
       <c r="E131" t="s">
-        <v>412</v>
+        <v>534</v>
       </c>
     </row>
     <row r="132">
@@ -4652,13 +4784,13 @@
         <v>0.18803911493869277</v>
       </c>
       <c r="C132" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D132" t="s">
-        <v>412</v>
+        <v>568</v>
       </c>
       <c r="E132" t="s">
-        <v>412</v>
+        <v>568</v>
       </c>
     </row>
     <row r="133">
@@ -4672,10 +4804,10 @@
         <v>416</v>
       </c>
       <c r="D133" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="E133" t="s">
-        <v>412</v>
+        <v>729</v>
       </c>
     </row>
     <row r="134">
@@ -4686,13 +4818,13 @@
         <v>0.18783045457017133</v>
       </c>
       <c r="C134" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D134" t="s">
-        <v>422</v>
+        <v>553</v>
       </c>
       <c r="E134" t="s">
-        <v>663</v>
+        <v>553</v>
       </c>
     </row>
     <row r="135">
@@ -4703,13 +4835,13 @@
         <v>0.1873579865710865</v>
       </c>
       <c r="C135" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="D135" t="s">
-        <v>562</v>
+        <v>454</v>
       </c>
       <c r="E135" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136">
@@ -4723,10 +4855,10 @@
         <v>417</v>
       </c>
       <c r="D136" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="E136" t="s">
-        <v>412</v>
+        <v>730</v>
       </c>
     </row>
     <row r="137">
@@ -4740,10 +4872,10 @@
         <v>405</v>
       </c>
       <c r="D137" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E137" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="138">
@@ -4754,13 +4886,13 @@
         <v>0.18638488112139323</v>
       </c>
       <c r="C138" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D138" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="E138" t="s">
-        <v>412</v>
+        <v>731</v>
       </c>
     </row>
     <row r="139">
@@ -4771,13 +4903,13 @@
         <v>0.18554765401851228</v>
       </c>
       <c r="C139" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D139" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="E139" t="s">
-        <v>412</v>
+        <v>732</v>
       </c>
     </row>
     <row r="140">
@@ -4788,13 +4920,13 @@
         <v>0.18520785095332887</v>
       </c>
       <c r="C140" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D140" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="E140" t="s">
-        <v>412</v>
+        <v>733</v>
       </c>
     </row>
     <row r="141">
@@ -4808,10 +4940,10 @@
         <v>407</v>
       </c>
       <c r="D141" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="E141" t="s">
-        <v>412</v>
+        <v>667</v>
       </c>
     </row>
     <row r="142">
@@ -4822,13 +4954,13 @@
         <v>0.18373983319012893</v>
       </c>
       <c r="C142" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D142" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="E142" t="s">
-        <v>715</v>
+        <v>734</v>
       </c>
     </row>
     <row r="143">
@@ -4842,10 +4974,10 @@
         <v>408</v>
       </c>
       <c r="D143" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E143" t="s">
-        <v>716</v>
+        <v>735</v>
       </c>
     </row>
     <row r="144">
@@ -4856,13 +4988,13 @@
         <v>0.18207794840805053</v>
       </c>
       <c r="C144" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D144" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E144" t="s">
-        <v>412</v>
+        <v>685</v>
       </c>
     </row>
     <row r="145">
@@ -4873,13 +5005,13 @@
         <v>0.18191464032471674</v>
       </c>
       <c r="C145" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D145" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="E145" t="s">
-        <v>717</v>
+        <v>736</v>
       </c>
     </row>
     <row r="146">
@@ -4890,13 +5022,13 @@
         <v>0.1816486924772337</v>
       </c>
       <c r="C146" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D146" t="s">
-        <v>412</v>
+        <v>574</v>
       </c>
       <c r="E146" t="s">
-        <v>412</v>
+        <v>574</v>
       </c>
     </row>
     <row r="147">
@@ -4910,10 +5042,10 @@
         <v>407</v>
       </c>
       <c r="D147" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E147" t="s">
-        <v>718</v>
+        <v>509</v>
       </c>
     </row>
     <row r="148">
@@ -4924,13 +5056,13 @@
         <v>0.18080879879386386</v>
       </c>
       <c r="C148" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D148" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="E148" t="s">
-        <v>719</v>
+        <v>737</v>
       </c>
     </row>
     <row r="149">
@@ -4944,10 +5076,10 @@
         <v>406</v>
       </c>
       <c r="D149" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E149" t="s">
-        <v>412</v>
+        <v>738</v>
       </c>
     </row>
     <row r="150">
@@ -4958,13 +5090,13 @@
         <v>0.1791363730375547</v>
       </c>
       <c r="C150" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E150" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="151">
@@ -4978,10 +5110,10 @@
         <v>420</v>
       </c>
       <c r="D151" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="E151" t="s">
-        <v>720</v>
+        <v>739</v>
       </c>
     </row>
     <row r="152">
@@ -4992,13 +5124,13 @@
         <v>0.1788607334044961</v>
       </c>
       <c r="C152" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="D152" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="E152" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
     </row>
     <row r="153">
@@ -5012,10 +5144,10 @@
         <v>406</v>
       </c>
       <c r="D153" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="E153" t="s">
-        <v>412</v>
+        <v>740</v>
       </c>
     </row>
     <row r="154">
@@ -5026,13 +5158,13 @@
         <v>0.1779240958799274</v>
       </c>
       <c r="C154" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D154" t="s">
-        <v>422</v>
+        <v>550</v>
       </c>
       <c r="E154" t="s">
-        <v>721</v>
+        <v>550</v>
       </c>
     </row>
     <row r="155">
@@ -5043,13 +5175,13 @@
         <v>0.17694614345223847</v>
       </c>
       <c r="C155" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="D155" t="s">
-        <v>568</v>
+        <v>425</v>
       </c>
       <c r="E155" t="s">
-        <v>722</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156">
@@ -5060,13 +5192,13 @@
         <v>0.17692275935241822</v>
       </c>
       <c r="C156" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D156" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="E156" t="s">
-        <v>412</v>
+        <v>741</v>
       </c>
     </row>
     <row r="157">
@@ -5077,13 +5209,13 @@
         <v>0.17631162481048246</v>
       </c>
       <c r="C157" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D157" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="E157" t="s">
-        <v>412</v>
+        <v>742</v>
       </c>
     </row>
     <row r="158">
@@ -5094,13 +5226,13 @@
         <v>0.17623129190883452</v>
       </c>
       <c r="C158" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D158" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="E158" t="s">
-        <v>412</v>
+        <v>743</v>
       </c>
     </row>
     <row r="159">
@@ -5111,13 +5243,13 @@
         <v>0.17621349182963753</v>
       </c>
       <c r="C159" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D159" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="E159" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
     </row>
     <row r="160">
@@ -5131,10 +5263,10 @@
         <v>405</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E160" t="s">
-        <v>724</v>
+        <v>515</v>
       </c>
     </row>
     <row r="161">
@@ -5145,13 +5277,13 @@
         <v>0.17544876225957917</v>
       </c>
       <c r="C161" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D161" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="E161" t="s">
-        <v>412</v>
+        <v>745</v>
       </c>
     </row>
     <row r="162">
@@ -5162,13 +5294,13 @@
         <v>0.17538889442090913</v>
       </c>
       <c r="C162" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="D162" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="E162" t="s">
-        <v>663</v>
+        <v>460</v>
       </c>
     </row>
     <row r="163">
@@ -5182,10 +5314,10 @@
         <v>405</v>
       </c>
       <c r="D163" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E163" t="s">
-        <v>725</v>
+        <v>515</v>
       </c>
     </row>
     <row r="164">
@@ -5196,13 +5328,13 @@
         <v>0.17495549140070113</v>
       </c>
       <c r="C164" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D164" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="E164" t="s">
-        <v>412</v>
+        <v>746</v>
       </c>
     </row>
     <row r="165">
@@ -5213,13 +5345,13 @@
         <v>0.1749165207753992</v>
       </c>
       <c r="C165" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="D165" t="s">
-        <v>575</v>
+        <v>454</v>
       </c>
       <c r="E165" t="s">
-        <v>726</v>
+        <v>454</v>
       </c>
     </row>
     <row r="166">
@@ -5233,10 +5365,10 @@
         <v>405</v>
       </c>
       <c r="D166" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E166" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="167">
@@ -5247,13 +5379,13 @@
         <v>0.1743799881190212</v>
       </c>
       <c r="C167" t="s">
-        <v>464</v>
+        <v>425</v>
       </c>
       <c r="D167" t="s">
-        <v>576</v>
+        <v>425</v>
       </c>
       <c r="E167" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="168">
@@ -5267,10 +5399,10 @@
         <v>406</v>
       </c>
       <c r="D168" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="E168" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
     </row>
     <row r="169">
@@ -5281,13 +5413,13 @@
         <v>0.17346087711308336</v>
       </c>
       <c r="C169" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D169" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="E169" t="s">
-        <v>412</v>
+        <v>748</v>
       </c>
     </row>
     <row r="170">
@@ -5298,13 +5430,13 @@
         <v>0.1731502128969787</v>
       </c>
       <c r="C170" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D170" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="E170" t="s">
-        <v>412</v>
+        <v>749</v>
       </c>
     </row>
     <row r="171">
@@ -5315,13 +5447,13 @@
         <v>0.17287853329542258</v>
       </c>
       <c r="C171" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D171" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E171" t="s">
-        <v>412</v>
+        <v>750</v>
       </c>
     </row>
     <row r="172">
@@ -5332,13 +5464,13 @@
         <v>0.1722584172546605</v>
       </c>
       <c r="C172" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="D172" t="s">
-        <v>552</v>
+        <v>425</v>
       </c>
       <c r="E172" t="s">
-        <v>728</v>
+        <v>425</v>
       </c>
     </row>
     <row r="173">
@@ -5352,10 +5484,10 @@
         <v>409</v>
       </c>
       <c r="D173" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="E173" t="s">
-        <v>729</v>
+        <v>521</v>
       </c>
     </row>
     <row r="174">
@@ -5369,10 +5501,10 @@
         <v>406</v>
       </c>
       <c r="D174" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="E174" t="s">
-        <v>412</v>
+        <v>751</v>
       </c>
     </row>
     <row r="175">
@@ -5383,13 +5515,13 @@
         <v>0.1718380184887022</v>
       </c>
       <c r="C175" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D175" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E175" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="176">
@@ -5400,13 +5532,13 @@
         <v>0.17146639478273085</v>
       </c>
       <c r="C176" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D176" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="E176" t="s">
-        <v>412</v>
+        <v>752</v>
       </c>
     </row>
     <row r="177">
@@ -5417,13 +5549,13 @@
         <v>0.17121147710729584</v>
       </c>
       <c r="C177" t="s">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="D177" t="s">
-        <v>412</v>
+        <v>464</v>
       </c>
       <c r="E177" t="s">
-        <v>412</v>
+        <v>464</v>
       </c>
     </row>
     <row r="178">
@@ -5434,13 +5566,13 @@
         <v>0.17112348692001325</v>
       </c>
       <c r="C178" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D178" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E178" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="179">
@@ -5454,10 +5586,10 @@
         <v>416</v>
       </c>
       <c r="D179" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="E179" t="s">
-        <v>412</v>
+        <v>753</v>
       </c>
     </row>
     <row r="180">
@@ -5471,10 +5603,10 @@
         <v>421</v>
       </c>
       <c r="D180" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="E180" t="s">
-        <v>412</v>
+        <v>754</v>
       </c>
     </row>
     <row r="181">
@@ -5485,13 +5617,13 @@
         <v>0.17056594460998556</v>
       </c>
       <c r="C181" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D181" t="s">
-        <v>412</v>
+        <v>590</v>
       </c>
       <c r="E181" t="s">
-        <v>412</v>
+        <v>590</v>
       </c>
     </row>
     <row r="182">
@@ -5502,13 +5634,13 @@
         <v>0.170292014181185</v>
       </c>
       <c r="C182" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D182" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="E182" t="s">
-        <v>412</v>
+        <v>755</v>
       </c>
     </row>
     <row r="183">
@@ -5522,10 +5654,10 @@
         <v>408</v>
       </c>
       <c r="D183" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E183" t="s">
-        <v>730</v>
+        <v>756</v>
       </c>
     </row>
     <row r="184">
@@ -5539,10 +5671,10 @@
         <v>407</v>
       </c>
       <c r="D184" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="E184" t="s">
-        <v>412</v>
+        <v>757</v>
       </c>
     </row>
     <row r="185">
@@ -5553,13 +5685,13 @@
         <v>0.16997575112855978</v>
       </c>
       <c r="C185" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D185" t="s">
-        <v>422</v>
+        <v>541</v>
       </c>
       <c r="E185" t="s">
-        <v>731</v>
+        <v>541</v>
       </c>
     </row>
     <row r="186">
@@ -5573,10 +5705,10 @@
         <v>405</v>
       </c>
       <c r="D186" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="E186" t="s">
-        <v>412</v>
+        <v>758</v>
       </c>
     </row>
     <row r="187">
@@ -5587,13 +5719,13 @@
         <v>0.16946664594851224</v>
       </c>
       <c r="C187" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D187" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="E187" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
     </row>
     <row r="188">
@@ -5607,10 +5739,10 @@
         <v>405</v>
       </c>
       <c r="D188" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E188" t="s">
-        <v>733</v>
+        <v>515</v>
       </c>
     </row>
     <row r="189">
@@ -5624,10 +5756,10 @@
         <v>405</v>
       </c>
       <c r="D189" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E189" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="190">
@@ -5641,10 +5773,10 @@
         <v>405</v>
       </c>
       <c r="D190" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E190" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="191">
@@ -5658,10 +5790,10 @@
         <v>417</v>
       </c>
       <c r="D191" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="E191" t="s">
-        <v>734</v>
+        <v>760</v>
       </c>
     </row>
     <row r="192">
@@ -5672,13 +5804,13 @@
         <v>0.16504740343026553</v>
       </c>
       <c r="C192" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D192" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="E192" t="s">
-        <v>735</v>
+        <v>761</v>
       </c>
     </row>
     <row r="193">
@@ -5692,10 +5824,10 @@
         <v>407</v>
       </c>
       <c r="D193" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E193" t="s">
-        <v>736</v>
+        <v>509</v>
       </c>
     </row>
     <row r="194">
@@ -5706,13 +5838,13 @@
         <v>0.16354510563362631</v>
       </c>
       <c r="C194" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D194" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="E194" t="s">
-        <v>412</v>
+        <v>762</v>
       </c>
     </row>
     <row r="195">
@@ -5723,13 +5855,13 @@
         <v>0.1628723617126877</v>
       </c>
       <c r="C195" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D195" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="E195" t="s">
-        <v>737</v>
+        <v>763</v>
       </c>
     </row>
     <row r="196">
@@ -5740,13 +5872,13 @@
         <v>0.1619196243184111</v>
       </c>
       <c r="C196" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D196" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E196" t="s">
-        <v>412</v>
+        <v>764</v>
       </c>
     </row>
     <row r="197">
@@ -5757,13 +5889,13 @@
         <v>0.16101911952026324</v>
       </c>
       <c r="C197" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D197" t="s">
-        <v>590</v>
+        <v>425</v>
       </c>
       <c r="E197" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="198">
@@ -5774,13 +5906,13 @@
         <v>0.1600347651269303</v>
       </c>
       <c r="C198" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D198" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="E198" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
     </row>
     <row r="199">
@@ -5791,13 +5923,13 @@
         <v>0.15991067653409138</v>
       </c>
       <c r="C199" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D199" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="E199" t="s">
-        <v>412</v>
+        <v>766</v>
       </c>
     </row>
     <row r="200">
@@ -5811,10 +5943,10 @@
         <v>415</v>
       </c>
       <c r="D200" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E200" t="s">
-        <v>739</v>
+        <v>767</v>
       </c>
     </row>
     <row r="201">
@@ -5825,13 +5957,13 @@
         <v>0.15937276188898272</v>
       </c>
       <c r="C201" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D201" t="s">
-        <v>593</v>
+        <v>423</v>
       </c>
       <c r="E201" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="202">
@@ -5842,13 +5974,13 @@
         <v>0.1591001483673892</v>
       </c>
       <c r="C202" t="s">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="D202" t="s">
-        <v>568</v>
+        <v>425</v>
       </c>
       <c r="E202" t="s">
-        <v>740</v>
+        <v>425</v>
       </c>
     </row>
     <row r="203">
@@ -5859,13 +5991,13 @@
         <v>0.15904572304240336</v>
       </c>
       <c r="C203" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D203" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E203" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="204">
@@ -5876,13 +6008,13 @@
         <v>0.15874375472187402</v>
       </c>
       <c r="C204" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D204" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="E204" t="s">
-        <v>741</v>
+        <v>768</v>
       </c>
     </row>
     <row r="205">
@@ -5896,10 +6028,10 @@
         <v>421</v>
       </c>
       <c r="D205" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="E205" t="s">
-        <v>412</v>
+        <v>769</v>
       </c>
     </row>
     <row r="206">
@@ -5913,10 +6045,10 @@
         <v>417</v>
       </c>
       <c r="D206" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="E206" t="s">
-        <v>742</v>
+        <v>770</v>
       </c>
     </row>
     <row r="207">
@@ -5927,13 +6059,13 @@
         <v>0.15717887336246314</v>
       </c>
       <c r="C207" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D207" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="E207" t="s">
-        <v>743</v>
+        <v>771</v>
       </c>
     </row>
     <row r="208">
@@ -5944,13 +6076,13 @@
         <v>0.15695492852957646</v>
       </c>
       <c r="C208" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D208" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E208" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="209">
@@ -5964,10 +6096,10 @@
         <v>409</v>
       </c>
       <c r="D209" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="E209" t="s">
-        <v>744</v>
+        <v>521</v>
       </c>
     </row>
     <row r="210">
@@ -5978,13 +6110,13 @@
         <v>0.1568184647436002</v>
       </c>
       <c r="C210" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D210" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E210" t="s">
-        <v>412</v>
+        <v>750</v>
       </c>
     </row>
     <row r="211">
@@ -5995,13 +6127,13 @@
         <v>0.15677644046133335</v>
       </c>
       <c r="C211" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D211" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E211" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212">
@@ -6012,13 +6144,13 @@
         <v>0.15655129948248056</v>
       </c>
       <c r="C212" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D212" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E212" t="s">
-        <v>412</v>
+        <v>772</v>
       </c>
     </row>
     <row r="213">
@@ -6029,13 +6161,13 @@
         <v>0.15644188571525974</v>
       </c>
       <c r="C213" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D213" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E213" t="s">
-        <v>745</v>
+        <v>773</v>
       </c>
     </row>
     <row r="214">
@@ -6046,13 +6178,13 @@
         <v>0.15641832051301782</v>
       </c>
       <c r="C214" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D214" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E214" t="s">
-        <v>746</v>
+        <v>774</v>
       </c>
     </row>
     <row r="215">
@@ -6063,13 +6195,13 @@
         <v>0.1564166202909617</v>
       </c>
       <c r="C215" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="D215" t="s">
-        <v>600</v>
+        <v>425</v>
       </c>
       <c r="E215" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="216">
@@ -6083,10 +6215,10 @@
         <v>405</v>
       </c>
       <c r="D216" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E216" t="s">
-        <v>747</v>
+        <v>775</v>
       </c>
     </row>
     <row r="217">
@@ -6100,10 +6232,10 @@
         <v>408</v>
       </c>
       <c r="D217" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E217" t="s">
-        <v>412</v>
+        <v>661</v>
       </c>
     </row>
     <row r="218">
@@ -6117,10 +6249,10 @@
         <v>421</v>
       </c>
       <c r="D218" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E218" t="s">
-        <v>748</v>
+        <v>776</v>
       </c>
     </row>
     <row r="219">
@@ -6131,13 +6263,13 @@
         <v>0.15545462041815297</v>
       </c>
       <c r="C219" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="D219" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="E219" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220">
@@ -6148,13 +6280,13 @@
         <v>0.15529031264300747</v>
       </c>
       <c r="C220" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D220" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E220" t="s">
-        <v>711</v>
+        <v>426</v>
       </c>
     </row>
     <row r="221">
@@ -6165,13 +6297,13 @@
         <v>0.15525833810376008</v>
       </c>
       <c r="C221" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="D221" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="E221" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="222">
@@ -6185,10 +6317,10 @@
         <v>407</v>
       </c>
       <c r="D222" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E222" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="223">
@@ -6199,13 +6331,13 @@
         <v>0.15507191103699905</v>
       </c>
       <c r="C223" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D223" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="E223" t="s">
-        <v>412</v>
+        <v>687</v>
       </c>
     </row>
     <row r="224">
@@ -6216,13 +6348,13 @@
         <v>0.15502770969433988</v>
       </c>
       <c r="C224" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="D224" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="E224" t="s">
-        <v>663</v>
+        <v>460</v>
       </c>
     </row>
     <row r="225">
@@ -6233,13 +6365,13 @@
         <v>0.1547949767646617</v>
       </c>
       <c r="C225" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D225" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E225" t="s">
-        <v>412</v>
+        <v>777</v>
       </c>
     </row>
     <row r="226">
@@ -6250,13 +6382,13 @@
         <v>0.15477040928343785</v>
       </c>
       <c r="C226" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D226" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="E226" t="s">
-        <v>412</v>
+        <v>766</v>
       </c>
     </row>
     <row r="227">
@@ -6267,13 +6399,13 @@
         <v>0.154742158706163</v>
       </c>
       <c r="C227" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D227" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E227" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="228">
@@ -6284,13 +6416,13 @@
         <v>0.15473046419557304</v>
       </c>
       <c r="C228" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D228" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E228" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="229">
@@ -6304,10 +6436,10 @@
         <v>416</v>
       </c>
       <c r="D229" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E229" t="s">
-        <v>412</v>
+        <v>778</v>
       </c>
     </row>
     <row r="230">
@@ -6321,10 +6453,10 @@
         <v>407</v>
       </c>
       <c r="D230" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="E230" t="s">
-        <v>412</v>
+        <v>779</v>
       </c>
     </row>
     <row r="231">
@@ -6338,10 +6470,10 @@
         <v>408</v>
       </c>
       <c r="D231" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E231" t="s">
-        <v>412</v>
+        <v>661</v>
       </c>
     </row>
     <row r="232">
@@ -6352,13 +6484,13 @@
         <v>0.15406816164726825</v>
       </c>
       <c r="C232" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D232" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E232" t="s">
-        <v>749</v>
+        <v>780</v>
       </c>
     </row>
     <row r="233">
@@ -6369,13 +6501,13 @@
         <v>0.15404909358096</v>
       </c>
       <c r="C233" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="D233" t="s">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c r="E233" t="s">
-        <v>663</v>
+        <v>460</v>
       </c>
     </row>
     <row r="234">
@@ -6386,13 +6518,13 @@
         <v>0.15359165211644438</v>
       </c>
       <c r="C234" t="s">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="D234" t="s">
-        <v>412</v>
+        <v>469</v>
       </c>
       <c r="E234" t="s">
-        <v>412</v>
+        <v>469</v>
       </c>
     </row>
     <row r="235">
@@ -6406,10 +6538,10 @@
         <v>418</v>
       </c>
       <c r="D235" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E235" t="s">
-        <v>412</v>
+        <v>781</v>
       </c>
     </row>
     <row r="236">
@@ -6420,13 +6552,13 @@
         <v>0.15347944959071924</v>
       </c>
       <c r="C236" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D236" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E236" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="237">
@@ -6440,10 +6572,10 @@
         <v>403</v>
       </c>
       <c r="D237" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E237" t="s">
-        <v>750</v>
+        <v>782</v>
       </c>
     </row>
     <row r="238">
@@ -6454,13 +6586,13 @@
         <v>0.15341371809169105</v>
       </c>
       <c r="C238" t="s">
-        <v>422</v>
+        <v>470</v>
       </c>
       <c r="D238" t="s">
-        <v>422</v>
+        <v>470</v>
       </c>
       <c r="E238" t="s">
-        <v>751</v>
+        <v>470</v>
       </c>
     </row>
     <row r="239">
@@ -6471,13 +6603,13 @@
         <v>0.15334491081589632</v>
       </c>
       <c r="C239" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D239" t="s">
-        <v>412</v>
+        <v>610</v>
       </c>
       <c r="E239" t="s">
-        <v>412</v>
+        <v>610</v>
       </c>
     </row>
     <row r="240">
@@ -6488,13 +6620,13 @@
         <v>0.1532893266357356</v>
       </c>
       <c r="C240" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D240" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="E240" t="s">
-        <v>412</v>
+        <v>783</v>
       </c>
     </row>
     <row r="241">
@@ -6505,13 +6637,13 @@
         <v>0.15328505328828637</v>
       </c>
       <c r="C241" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="D241" t="s">
-        <v>608</v>
+        <v>472</v>
       </c>
       <c r="E241" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
     </row>
     <row r="242">
@@ -6522,13 +6654,13 @@
         <v>0.15328375553126064</v>
       </c>
       <c r="C242" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D242" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E242" t="s">
-        <v>752</v>
+        <v>784</v>
       </c>
     </row>
     <row r="243">
@@ -6539,13 +6671,13 @@
         <v>0.15322051988921911</v>
       </c>
       <c r="C243" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D243" t="s">
-        <v>412</v>
+        <v>613</v>
       </c>
       <c r="E243" t="s">
-        <v>412</v>
+        <v>613</v>
       </c>
     </row>
     <row r="244">
@@ -6556,13 +6688,13 @@
         <v>0.1532113439089142</v>
       </c>
       <c r="C244" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D244" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="E244" t="s">
-        <v>753</v>
+        <v>785</v>
       </c>
     </row>
     <row r="245">
@@ -6573,13 +6705,13 @@
         <v>0.15301908460040167</v>
       </c>
       <c r="C245" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D245" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="E245" t="s">
-        <v>412</v>
+        <v>786</v>
       </c>
     </row>
     <row r="246">
@@ -6590,13 +6722,13 @@
         <v>0.15299875494520446</v>
       </c>
       <c r="C246" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D246" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E246" t="s">
-        <v>754</v>
+        <v>426</v>
       </c>
     </row>
     <row r="247">
@@ -6607,13 +6739,13 @@
         <v>0.15294433499990479</v>
       </c>
       <c r="C247" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D247" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E247" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="248">
@@ -6624,13 +6756,13 @@
         <v>0.1529374486483654</v>
       </c>
       <c r="C248" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="D248" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="E248" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
     </row>
     <row r="249">
@@ -6641,13 +6773,13 @@
         <v>0.15291273505213956</v>
       </c>
       <c r="C249" t="s">
-        <v>412</v>
+        <v>475</v>
       </c>
       <c r="D249" t="s">
-        <v>412</v>
+        <v>475</v>
       </c>
       <c r="E249" t="s">
-        <v>412</v>
+        <v>475</v>
       </c>
     </row>
     <row r="250">
@@ -6658,13 +6790,13 @@
         <v>0.15280864243232517</v>
       </c>
       <c r="C250" t="s">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="D250" t="s">
-        <v>611</v>
+        <v>468</v>
       </c>
       <c r="E250" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
     </row>
     <row r="251">
@@ -6678,10 +6810,10 @@
         <v>406</v>
       </c>
       <c r="D251" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="E251" t="s">
-        <v>412</v>
+        <v>719</v>
       </c>
     </row>
     <row r="252">
@@ -6692,13 +6824,13 @@
         <v>0.15274856020467772</v>
       </c>
       <c r="C252" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D252" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E252" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="253">
@@ -6709,13 +6841,13 @@
         <v>0.1526599103818144</v>
       </c>
       <c r="C253" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="D253" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="E253" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="254">
@@ -6726,13 +6858,13 @@
         <v>0.15265048304365528</v>
       </c>
       <c r="C254" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="D254" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="E254" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="255">
@@ -6743,13 +6875,13 @@
         <v>0.15261215747365905</v>
       </c>
       <c r="C255" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D255" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="E255" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
     </row>
     <row r="256">
@@ -6760,13 +6892,13 @@
         <v>0.1526028770265465</v>
       </c>
       <c r="C256" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D256" t="s">
-        <v>412</v>
+        <v>615</v>
       </c>
       <c r="E256" t="s">
-        <v>412</v>
+        <v>615</v>
       </c>
     </row>
     <row r="257">
@@ -6777,13 +6909,13 @@
         <v>0.1525531812706453</v>
       </c>
       <c r="C257" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D257" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E257" t="s">
-        <v>756</v>
+        <v>788</v>
       </c>
     </row>
     <row r="258">
@@ -6794,13 +6926,13 @@
         <v>0.1525467720804749</v>
       </c>
       <c r="C258" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="D258" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="E258" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
     </row>
     <row r="259">
@@ -6811,13 +6943,13 @@
         <v>0.15253174782894946</v>
       </c>
       <c r="C259" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D259" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="E259" t="s">
-        <v>412</v>
+        <v>789</v>
       </c>
     </row>
     <row r="260">
@@ -6828,13 +6960,13 @@
         <v>0.15244689879588477</v>
       </c>
       <c r="C260" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="D260" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="E260" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
     </row>
     <row r="261">
@@ -6845,13 +6977,13 @@
         <v>0.152411973006043</v>
       </c>
       <c r="C261" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="D261" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="E261" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="262">
@@ -6862,13 +6994,13 @@
         <v>0.15240297398856978</v>
       </c>
       <c r="C262" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="D262" t="s">
-        <v>613</v>
+        <v>425</v>
       </c>
       <c r="E262" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="263">
@@ -6879,13 +7011,13 @@
         <v>0.15229754210585641</v>
       </c>
       <c r="C263" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D263" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E263" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="264">
@@ -6899,10 +7031,10 @@
         <v>406</v>
       </c>
       <c r="D264" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="E264" t="s">
-        <v>412</v>
+        <v>790</v>
       </c>
     </row>
     <row r="265">
@@ -6913,13 +7045,13 @@
         <v>0.15221096074430504</v>
       </c>
       <c r="C265" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="D265" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="E265" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="266">
@@ -6930,13 +7062,13 @@
         <v>0.1521627931048417</v>
       </c>
       <c r="C266" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="D266" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E266" t="s">
-        <v>757</v>
+        <v>791</v>
       </c>
     </row>
     <row r="267">
@@ -6947,13 +7079,13 @@
         <v>0.15213061087794796</v>
       </c>
       <c r="C267" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D267" t="s">
-        <v>412</v>
+        <v>619</v>
       </c>
       <c r="E267" t="s">
-        <v>412</v>
+        <v>619</v>
       </c>
     </row>
     <row r="268">
@@ -6967,10 +7099,10 @@
         <v>405</v>
       </c>
       <c r="D268" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E268" t="s">
-        <v>412</v>
+        <v>792</v>
       </c>
     </row>
     <row r="269">
@@ -6981,13 +7113,13 @@
         <v>0.15199857785564028</v>
       </c>
       <c r="C269" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D269" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="E269" t="s">
-        <v>412</v>
+        <v>793</v>
       </c>
     </row>
     <row r="270">
@@ -6998,13 +7130,13 @@
         <v>0.15199119318145168</v>
       </c>
       <c r="C270" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="D270" t="s">
-        <v>542</v>
+        <v>425</v>
       </c>
       <c r="E270" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="271">
@@ -7015,13 +7147,13 @@
         <v>0.1519832857740994</v>
       </c>
       <c r="C271" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D271" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="E271" t="s">
-        <v>412</v>
+        <v>794</v>
       </c>
     </row>
     <row r="272">
@@ -7035,10 +7167,10 @@
         <v>408</v>
       </c>
       <c r="D272" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E272" t="s">
-        <v>758</v>
+        <v>795</v>
       </c>
     </row>
     <row r="273">
@@ -7049,13 +7181,13 @@
         <v>0.15187792499224054</v>
       </c>
       <c r="C273" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D273" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E273" t="s">
-        <v>759</v>
+        <v>796</v>
       </c>
     </row>
     <row r="274">
@@ -7066,13 +7198,13 @@
         <v>0.1517070426866383</v>
       </c>
       <c r="C274" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D274" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E274" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="275">
@@ -7083,13 +7215,13 @@
         <v>0.15163015712928224</v>
       </c>
       <c r="C275" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D275" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="E275" t="s">
-        <v>412</v>
+        <v>797</v>
       </c>
     </row>
     <row r="276">
@@ -7100,13 +7232,13 @@
         <v>0.15159282821813308</v>
       </c>
       <c r="C276" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D276" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E276" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="277">
@@ -7117,13 +7249,13 @@
         <v>0.15158907514768039</v>
       </c>
       <c r="C277" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D277" t="s">
-        <v>412</v>
+        <v>610</v>
       </c>
       <c r="E277" t="s">
-        <v>412</v>
+        <v>610</v>
       </c>
     </row>
     <row r="278">
@@ -7134,13 +7266,13 @@
         <v>0.1515291540553129</v>
       </c>
       <c r="C278" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D278" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E278" t="s">
-        <v>412</v>
+        <v>798</v>
       </c>
     </row>
     <row r="279">
@@ -7151,13 +7283,13 @@
         <v>0.15144790201221742</v>
       </c>
       <c r="C279" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="D279" t="s">
-        <v>542</v>
+        <v>425</v>
       </c>
       <c r="E279" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="280">
@@ -7168,13 +7300,13 @@
         <v>0.15134230917056576</v>
       </c>
       <c r="C280" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D280" t="s">
-        <v>412</v>
+        <v>626</v>
       </c>
       <c r="E280" t="s">
-        <v>412</v>
+        <v>626</v>
       </c>
     </row>
     <row r="281">
@@ -7188,10 +7320,10 @@
         <v>407</v>
       </c>
       <c r="D281" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E281" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="282">
@@ -7202,13 +7334,13 @@
         <v>0.15123830153247297</v>
       </c>
       <c r="C282" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="D282" t="s">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="E282" t="s">
-        <v>760</v>
+        <v>452</v>
       </c>
     </row>
     <row r="283">
@@ -7219,13 +7351,13 @@
         <v>0.15123654756720756</v>
       </c>
       <c r="C283" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D283" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="E283" t="s">
-        <v>412</v>
+        <v>799</v>
       </c>
     </row>
     <row r="284">
@@ -7236,13 +7368,13 @@
         <v>0.15122037742441025</v>
       </c>
       <c r="C284" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="D284" t="s">
-        <v>623</v>
+        <v>472</v>
       </c>
       <c r="E284" t="s">
-        <v>761</v>
+        <v>472</v>
       </c>
     </row>
     <row r="285">
@@ -7270,13 +7402,13 @@
         <v>0.15115570088307326</v>
       </c>
       <c r="C286" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="D286" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="E286" t="s">
-        <v>412</v>
+        <v>800</v>
       </c>
     </row>
     <row r="287">
@@ -7287,13 +7419,13 @@
         <v>0.15111515568584744</v>
       </c>
       <c r="C287" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D287" t="s">
-        <v>533</v>
+        <v>425</v>
       </c>
       <c r="E287" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="288">
@@ -7304,13 +7436,13 @@
         <v>0.1510646937503987</v>
       </c>
       <c r="C288" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="D288" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="E288" t="s">
-        <v>762</v>
+        <v>801</v>
       </c>
     </row>
     <row r="289">
@@ -7321,13 +7453,13 @@
         <v>0.1510059242847932</v>
       </c>
       <c r="C289" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="D289" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="E289" t="s">
-        <v>412</v>
+        <v>802</v>
       </c>
     </row>
     <row r="290">
@@ -7341,10 +7473,10 @@
         <v>401</v>
       </c>
       <c r="D290" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E290" t="s">
-        <v>763</v>
+        <v>803</v>
       </c>
     </row>
     <row r="291">
@@ -7355,13 +7487,13 @@
         <v>0.1509219550487203</v>
       </c>
       <c r="C291" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D291" t="s">
-        <v>412</v>
+        <v>632</v>
       </c>
       <c r="E291" t="s">
-        <v>412</v>
+        <v>632</v>
       </c>
     </row>
     <row r="292">
@@ -7372,13 +7504,13 @@
         <v>0.15089237725554255</v>
       </c>
       <c r="C292" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D292" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="E292" t="s">
-        <v>412</v>
+        <v>804</v>
       </c>
     </row>
     <row r="293">
@@ -7389,13 +7521,13 @@
         <v>0.1508834819106143</v>
       </c>
       <c r="C293" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="D293" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="E293" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="294">
@@ -7406,13 +7538,13 @@
         <v>0.1508105290193314</v>
       </c>
       <c r="C294" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D294" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E294" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="295">
@@ -7423,13 +7555,13 @@
         <v>0.15076215963934692</v>
       </c>
       <c r="C295" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D295" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E295" t="s">
-        <v>412</v>
+        <v>805</v>
       </c>
     </row>
     <row r="296">
@@ -7440,13 +7572,13 @@
         <v>0.1507406247149899</v>
       </c>
       <c r="C296" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D296" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E296" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="297">
@@ -7457,13 +7589,13 @@
         <v>0.1507383880904431</v>
       </c>
       <c r="C297" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="D297" t="s">
-        <v>552</v>
+        <v>425</v>
       </c>
       <c r="E297" t="s">
-        <v>764</v>
+        <v>425</v>
       </c>
     </row>
     <row r="298">
@@ -7474,13 +7606,13 @@
         <v>0.15072286281878222</v>
       </c>
       <c r="C298" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="D298" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="E298" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
     </row>
     <row r="299">
@@ -7491,13 +7623,13 @@
         <v>0.1507116514834478</v>
       </c>
       <c r="C299" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D299" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E299" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="300">
@@ -7508,13 +7640,13 @@
         <v>0.15066019247096907</v>
       </c>
       <c r="C300" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="D300" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
       <c r="E300" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
     </row>
     <row r="301">
@@ -7525,13 +7657,13 @@
         <v>0.15065960496767483</v>
       </c>
       <c r="C301" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D301" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E301" t="s">
-        <v>765</v>
+        <v>806</v>
       </c>
     </row>
     <row r="302">
@@ -7542,13 +7674,13 @@
         <v>0.15063490220909542</v>
       </c>
       <c r="C302" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D302" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="E302" t="s">
-        <v>766</v>
+        <v>807</v>
       </c>
     </row>
     <row r="303">
@@ -7562,10 +7694,10 @@
         <v>411</v>
       </c>
       <c r="D303" t="s">
-        <v>412</v>
+        <v>634</v>
       </c>
       <c r="E303" t="s">
-        <v>412</v>
+        <v>634</v>
       </c>
     </row>
     <row r="304">
@@ -7576,13 +7708,13 @@
         <v>0.15059998633186014</v>
       </c>
       <c r="C304" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D304" t="s">
-        <v>412</v>
+        <v>488</v>
       </c>
       <c r="E304" t="s">
-        <v>412</v>
+        <v>488</v>
       </c>
     </row>
     <row r="305">
@@ -7593,13 +7725,13 @@
         <v>0.15059791036430378</v>
       </c>
       <c r="C305" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D305" t="s">
-        <v>412</v>
+        <v>635</v>
       </c>
       <c r="E305" t="s">
-        <v>412</v>
+        <v>635</v>
       </c>
     </row>
     <row r="306">
@@ -7610,13 +7742,13 @@
         <v>0.1505398361253645</v>
       </c>
       <c r="C306" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D306" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E306" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="307">
@@ -7630,10 +7762,10 @@
         <v>407</v>
       </c>
       <c r="D307" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="E307" t="s">
-        <v>412</v>
+        <v>667</v>
       </c>
     </row>
     <row r="308">
@@ -7644,13 +7776,13 @@
         <v>0.15052106509111135</v>
       </c>
       <c r="C308" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D308" t="s">
-        <v>412</v>
+        <v>636</v>
       </c>
       <c r="E308" t="s">
-        <v>412</v>
+        <v>636</v>
       </c>
     </row>
     <row r="309">
@@ -7661,13 +7793,13 @@
         <v>0.15051222268073675</v>
       </c>
       <c r="C309" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D309" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E309" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="310">
@@ -7678,13 +7810,13 @@
         <v>0.15049963403487893</v>
       </c>
       <c r="C310" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="D310" t="s">
-        <v>629</v>
+        <v>437</v>
       </c>
       <c r="E310" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
     </row>
     <row r="311">
@@ -7695,13 +7827,13 @@
         <v>0.15048718454895663</v>
       </c>
       <c r="C311" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="D311" t="s">
-        <v>613</v>
+        <v>425</v>
       </c>
       <c r="E311" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="312">
@@ -7715,10 +7847,10 @@
         <v>422</v>
       </c>
       <c r="D312" t="s">
-        <v>630</v>
+        <v>422</v>
       </c>
       <c r="E312" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="313">
@@ -7729,13 +7861,13 @@
         <v>0.15043637716091024</v>
       </c>
       <c r="C313" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="D313" t="s">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="E313" t="s">
-        <v>767</v>
+        <v>447</v>
       </c>
     </row>
     <row r="314">
@@ -7746,13 +7878,13 @@
         <v>0.15037976462121236</v>
       </c>
       <c r="C314" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="D314" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="E314" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="315">
@@ -7763,13 +7895,13 @@
         <v>0.15037946533148022</v>
       </c>
       <c r="C315" t="s">
-        <v>412</v>
+        <v>491</v>
       </c>
       <c r="D315" t="s">
-        <v>412</v>
+        <v>491</v>
       </c>
       <c r="E315" t="s">
-        <v>412</v>
+        <v>491</v>
       </c>
     </row>
     <row r="316">
@@ -7780,13 +7912,13 @@
         <v>0.15031888373126936</v>
       </c>
       <c r="C316" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="D316" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="E316" t="s">
-        <v>412</v>
+        <v>808</v>
       </c>
     </row>
     <row r="317">
@@ -7797,13 +7929,13 @@
         <v>0.15030308444899976</v>
       </c>
       <c r="C317" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D317" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E317" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="318">
@@ -7817,10 +7949,10 @@
         <v>416</v>
       </c>
       <c r="D318" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="E318" t="s">
-        <v>412</v>
+        <v>809</v>
       </c>
     </row>
     <row r="319">
@@ -7831,13 +7963,13 @@
         <v>0.15027684405043976</v>
       </c>
       <c r="C319" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D319" t="s">
-        <v>412</v>
+        <v>626</v>
       </c>
       <c r="E319" t="s">
-        <v>412</v>
+        <v>626</v>
       </c>
     </row>
     <row r="320">
@@ -7848,13 +7980,13 @@
         <v>0.15027063180423197</v>
       </c>
       <c r="C320" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="D320" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="E320" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
     </row>
     <row r="321">
@@ -7865,13 +7997,13 @@
         <v>0.15025674891209007</v>
       </c>
       <c r="C321" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D321" t="s">
-        <v>412</v>
+        <v>615</v>
       </c>
       <c r="E321" t="s">
-        <v>412</v>
+        <v>615</v>
       </c>
     </row>
     <row r="322">
@@ -7882,13 +8014,13 @@
         <v>0.1502066262246968</v>
       </c>
       <c r="C322" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="D322" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="E322" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="323">
@@ -7902,10 +8034,10 @@
         <v>405</v>
       </c>
       <c r="D323" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E323" t="s">
-        <v>412</v>
+        <v>810</v>
       </c>
     </row>
     <row r="324">
@@ -7916,13 +8048,13 @@
         <v>0.150164441638144</v>
       </c>
       <c r="C324" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D324" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E324" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="325">
@@ -7933,13 +8065,13 @@
         <v>0.15014312310395456</v>
       </c>
       <c r="C325" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="D325" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="E325" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
     </row>
     <row r="326">
@@ -7950,13 +8082,13 @@
         <v>0.15012704455927747</v>
       </c>
       <c r="C326" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D326" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E326" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="327">
@@ -7970,10 +8102,10 @@
         <v>408</v>
       </c>
       <c r="D327" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E327" t="s">
-        <v>768</v>
+        <v>811</v>
       </c>
     </row>
     <row r="328">
@@ -7984,13 +8116,13 @@
         <v>0.15010930177967619</v>
       </c>
       <c r="C328" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D328" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E328" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="329">
@@ -8001,13 +8133,13 @@
         <v>0.15005769954917153</v>
       </c>
       <c r="C329" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D329" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E329" t="s">
-        <v>412</v>
+        <v>812</v>
       </c>
     </row>
     <row r="330">
@@ -8021,10 +8153,10 @@
         <v>418</v>
       </c>
       <c r="D330" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="E330" t="s">
-        <v>412</v>
+        <v>813</v>
       </c>
     </row>
     <row r="331">
@@ -8035,13 +8167,13 @@
         <v>0.14999197965612315</v>
       </c>
       <c r="C331" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D331" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E331" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="332">
@@ -8052,13 +8184,13 @@
         <v>0.14998508407000438</v>
       </c>
       <c r="C332" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="D332" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="E332" t="s">
-        <v>769</v>
+        <v>814</v>
       </c>
     </row>
     <row r="333">
@@ -8069,13 +8201,13 @@
         <v>0.1499444481959969</v>
       </c>
       <c r="C333" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D333" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="E333" t="s">
-        <v>770</v>
+        <v>815</v>
       </c>
     </row>
     <row r="334">
@@ -8086,13 +8218,13 @@
         <v>0.14993192548160356</v>
       </c>
       <c r="C334" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D334" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E334" t="s">
-        <v>412</v>
+        <v>750</v>
       </c>
     </row>
     <row r="335">
@@ -8103,13 +8235,13 @@
         <v>0.14983295757242568</v>
       </c>
       <c r="C335" t="s">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="D335" t="s">
-        <v>638</v>
+        <v>495</v>
       </c>
       <c r="E335" t="s">
-        <v>412</v>
+        <v>495</v>
       </c>
     </row>
     <row r="336">
@@ -8120,13 +8252,13 @@
         <v>0.1498030984015302</v>
       </c>
       <c r="C336" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D336" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E336" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="337">
@@ -8137,13 +8269,13 @@
         <v>0.1498006148623599</v>
       </c>
       <c r="C337" t="s">
-        <v>412</v>
+        <v>496</v>
       </c>
       <c r="D337" t="s">
-        <v>412</v>
+        <v>496</v>
       </c>
       <c r="E337" t="s">
-        <v>412</v>
+        <v>496</v>
       </c>
     </row>
     <row r="338">
@@ -8154,13 +8286,13 @@
         <v>0.14979057177356953</v>
       </c>
       <c r="C338" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="D338" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="E338" t="s">
-        <v>412</v>
+        <v>816</v>
       </c>
     </row>
     <row r="339">
@@ -8171,13 +8303,13 @@
         <v>0.14975838964398203</v>
       </c>
       <c r="C339" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="D339" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="E339" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="340">
@@ -8188,13 +8320,13 @@
         <v>0.14975529109018804</v>
       </c>
       <c r="C340" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D340" t="s">
-        <v>640</v>
+        <v>425</v>
       </c>
       <c r="E340" t="s">
-        <v>771</v>
+        <v>425</v>
       </c>
     </row>
     <row r="341">
@@ -8205,13 +8337,13 @@
         <v>0.14973496589178573</v>
       </c>
       <c r="C341" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D341" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E341" t="s">
-        <v>412</v>
+        <v>817</v>
       </c>
     </row>
     <row r="342">
@@ -8225,10 +8357,10 @@
         <v>407</v>
       </c>
       <c r="D342" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="E342" t="s">
-        <v>412</v>
+        <v>757</v>
       </c>
     </row>
     <row r="343">
@@ -8239,13 +8371,13 @@
         <v>0.14967700874959444</v>
       </c>
       <c r="C343" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="D343" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
       <c r="E343" t="s">
-        <v>412</v>
+        <v>454</v>
       </c>
     </row>
     <row r="344">
@@ -8256,13 +8388,13 @@
         <v>0.14960696989735695</v>
       </c>
       <c r="C344" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D344" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E344" t="s">
-        <v>412</v>
+        <v>722</v>
       </c>
     </row>
     <row r="345">
@@ -8273,13 +8405,13 @@
         <v>0.1496011647462597</v>
       </c>
       <c r="C345" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D345" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E345" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="346">
@@ -8290,13 +8422,13 @@
         <v>0.1495042065610581</v>
       </c>
       <c r="C346" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D346" t="s">
-        <v>641</v>
+        <v>487</v>
       </c>
       <c r="E346" t="s">
-        <v>412</v>
+        <v>487</v>
       </c>
     </row>
     <row r="347">
@@ -8307,13 +8439,13 @@
         <v>0.14941590289586812</v>
       </c>
       <c r="C347" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D347" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="E347" t="s">
-        <v>772</v>
+        <v>818</v>
       </c>
     </row>
     <row r="348">
@@ -8324,13 +8456,13 @@
         <v>0.14941353731217685</v>
       </c>
       <c r="C348" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D348" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E348" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="349">
@@ -8344,10 +8476,10 @@
         <v>407</v>
       </c>
       <c r="D349" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E349" t="s">
-        <v>663</v>
+        <v>701</v>
       </c>
     </row>
     <row r="350">
@@ -8358,13 +8490,13 @@
         <v>0.14919239872302634</v>
       </c>
       <c r="C350" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D350" t="s">
-        <v>422</v>
+        <v>564</v>
       </c>
       <c r="E350" t="s">
-        <v>773</v>
+        <v>564</v>
       </c>
     </row>
     <row r="351">
@@ -8378,10 +8510,10 @@
         <v>405</v>
       </c>
       <c r="D351" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="E351" t="s">
-        <v>412</v>
+        <v>819</v>
       </c>
     </row>
     <row r="352">
@@ -8392,13 +8524,13 @@
         <v>0.14903579990271962</v>
       </c>
       <c r="C352" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="D352" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="E352" t="s">
-        <v>774</v>
+        <v>472</v>
       </c>
     </row>
     <row r="353">
@@ -8412,10 +8544,10 @@
         <v>421</v>
       </c>
       <c r="D353" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="E353" t="s">
-        <v>775</v>
+        <v>820</v>
       </c>
     </row>
     <row r="354">
@@ -8426,13 +8558,13 @@
         <v>0.14876636412167668</v>
       </c>
       <c r="C354" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D354" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
       <c r="E354" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
     </row>
     <row r="355">
@@ -8443,13 +8575,13 @@
         <v>0.14851964878525742</v>
       </c>
       <c r="C355" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D355" t="s">
-        <v>412</v>
+        <v>646</v>
       </c>
       <c r="E355" t="s">
-        <v>412</v>
+        <v>646</v>
       </c>
     </row>
     <row r="356">
@@ -8463,10 +8595,10 @@
         <v>405</v>
       </c>
       <c r="D356" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E356" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="357">
@@ -8477,13 +8609,13 @@
         <v>0.148343830865817</v>
       </c>
       <c r="C357" t="s">
-        <v>491</v>
+        <v>425</v>
       </c>
       <c r="D357" t="s">
-        <v>643</v>
+        <v>425</v>
       </c>
       <c r="E357" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="358">
@@ -8494,13 +8626,13 @@
         <v>0.1483002889037324</v>
       </c>
       <c r="C358" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D358" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E358" t="s">
-        <v>776</v>
+        <v>821</v>
       </c>
     </row>
     <row r="359">
@@ -8514,10 +8646,10 @@
         <v>405</v>
       </c>
       <c r="D359" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E359" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="360">
@@ -8531,10 +8663,10 @@
         <v>405</v>
       </c>
       <c r="D360" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="E360" t="s">
-        <v>412</v>
+        <v>810</v>
       </c>
     </row>
     <row r="361">
@@ -8545,13 +8677,13 @@
         <v>0.14811514385185442</v>
       </c>
       <c r="C361" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D361" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
       <c r="E361" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
     </row>
     <row r="362">
@@ -8562,13 +8694,13 @@
         <v>0.14800913342084385</v>
       </c>
       <c r="C362" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D362" t="s">
-        <v>412</v>
+        <v>647</v>
       </c>
       <c r="E362" t="s">
-        <v>412</v>
+        <v>647</v>
       </c>
     </row>
     <row r="363">
@@ -8579,13 +8711,13 @@
         <v>0.14799165395457473</v>
       </c>
       <c r="C363" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D363" t="s">
-        <v>412</v>
+        <v>648</v>
       </c>
       <c r="E363" t="s">
-        <v>412</v>
+        <v>648</v>
       </c>
     </row>
     <row r="364">
@@ -8596,13 +8728,13 @@
         <v>0.14786750505613946</v>
       </c>
       <c r="C364" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D364" t="s">
-        <v>412</v>
+        <v>553</v>
       </c>
       <c r="E364" t="s">
-        <v>412</v>
+        <v>553</v>
       </c>
     </row>
     <row r="365">
@@ -8616,10 +8748,10 @@
         <v>407</v>
       </c>
       <c r="D365" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E365" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="366">
@@ -8633,10 +8765,10 @@
         <v>405</v>
       </c>
       <c r="D366" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E366" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="367">
@@ -8647,13 +8779,13 @@
         <v>0.14751272601984888</v>
       </c>
       <c r="C367" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D367" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E367" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="368">
@@ -8664,13 +8796,13 @@
         <v>0.14725038080645514</v>
       </c>
       <c r="C368" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D368" t="s">
-        <v>644</v>
+        <v>426</v>
       </c>
       <c r="E368" t="s">
-        <v>777</v>
+        <v>426</v>
       </c>
     </row>
     <row r="369">
@@ -8681,13 +8813,13 @@
         <v>0.146900890820796</v>
       </c>
       <c r="C369" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D369" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
       <c r="E369" t="s">
-        <v>412</v>
+        <v>564</v>
       </c>
     </row>
     <row r="370">
@@ -8698,13 +8830,13 @@
         <v>0.14680242710899816</v>
       </c>
       <c r="C370" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="D370" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="E370" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
     </row>
     <row r="371">
@@ -8718,10 +8850,10 @@
         <v>405</v>
       </c>
       <c r="D371" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
       <c r="E371" t="s">
-        <v>412</v>
+        <v>515</v>
       </c>
     </row>
     <row r="372">
@@ -8735,10 +8867,10 @@
         <v>415</v>
       </c>
       <c r="D372" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E372" t="s">
-        <v>412</v>
+        <v>694</v>
       </c>
     </row>
     <row r="373">
@@ -8749,13 +8881,13 @@
         <v>0.14556230967990189</v>
       </c>
       <c r="C373" t="s">
-        <v>412</v>
+        <v>500</v>
       </c>
       <c r="D373" t="s">
-        <v>412</v>
+        <v>500</v>
       </c>
       <c r="E373" t="s">
-        <v>412</v>
+        <v>500</v>
       </c>
     </row>
     <row r="374">
@@ -8769,10 +8901,10 @@
         <v>415</v>
       </c>
       <c r="D374" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E374" t="s">
-        <v>412</v>
+        <v>694</v>
       </c>
     </row>
     <row r="375">
@@ -8783,13 +8915,13 @@
         <v>0.14401540138546448</v>
       </c>
       <c r="C375" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D375" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E375" t="s">
-        <v>412</v>
+        <v>822</v>
       </c>
     </row>
     <row r="376">
@@ -8803,10 +8935,10 @@
         <v>407</v>
       </c>
       <c r="D376" t="s">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="E376" t="s">
-        <v>778</v>
+        <v>509</v>
       </c>
     </row>
     <row r="377">
@@ -8820,10 +8952,10 @@
         <v>409</v>
       </c>
       <c r="D377" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="E377" t="s">
-        <v>665</v>
+        <v>521</v>
       </c>
     </row>
     <row r="378">
@@ -8834,13 +8966,13 @@
         <v>0.14246507347931137</v>
       </c>
       <c r="C378" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="D378" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E378" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="379">
@@ -8851,13 +8983,13 @@
         <v>0.13978549673269777</v>
       </c>
       <c r="C379" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D379" t="s">
-        <v>412</v>
+        <v>590</v>
       </c>
       <c r="E379" t="s">
-        <v>412</v>
+        <v>590</v>
       </c>
     </row>
     <row r="380">
@@ -8868,13 +9000,13 @@
         <v>0.13948994760951378</v>
       </c>
       <c r="C380" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D380" t="s">
-        <v>412</v>
+        <v>647</v>
       </c>
       <c r="E380" t="s">
-        <v>412</v>
+        <v>647</v>
       </c>
     </row>
     <row r="381">
@@ -8888,10 +9020,10 @@
         <v>421</v>
       </c>
       <c r="D381" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="E381" t="s">
-        <v>412</v>
+        <v>823</v>
       </c>
     </row>
     <row r="382">
@@ -8905,10 +9037,10 @@
         <v>405</v>
       </c>
       <c r="D382" t="s">
-        <v>422</v>
+        <v>515</v>
       </c>
       <c r="E382" t="s">
-        <v>779</v>
+        <v>515</v>
       </c>
     </row>
     <row r="383">
@@ -8919,13 +9051,13 @@
         <v>0.13642844010480792</v>
       </c>
       <c r="C383" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="D383" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="E383" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="384">
@@ -8939,10 +9071,10 @@
         <v>418</v>
       </c>
       <c r="D384" t="s">
-        <v>422</v>
+        <v>650</v>
       </c>
       <c r="E384" t="s">
-        <v>780</v>
+        <v>650</v>
       </c>
     </row>
     <row r="385">
@@ -8953,13 +9085,13 @@
         <v>0.13240445326465683</v>
       </c>
       <c r="C385" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D385" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="E385" t="s">
-        <v>781</v>
+        <v>824</v>
       </c>
     </row>
     <row r="386">
@@ -8970,13 +9102,13 @@
         <v>0.13119252063560116</v>
       </c>
       <c r="C386" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D386" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="E386" t="s">
-        <v>412</v>
+        <v>825</v>
       </c>
     </row>
     <row r="387">
@@ -8990,10 +9122,10 @@
         <v>409</v>
       </c>
       <c r="D387" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="E387" t="s">
-        <v>782</v>
+        <v>521</v>
       </c>
     </row>
     <row r="388">
@@ -9004,13 +9136,13 @@
         <v>0.13064512169238274</v>
       </c>
       <c r="C388" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D388" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="E388" t="s">
-        <v>412</v>
+        <v>826</v>
       </c>
     </row>
     <row r="389">
@@ -9024,10 +9156,10 @@
         <v>414</v>
       </c>
       <c r="D389" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="E389" t="s">
-        <v>412</v>
+        <v>827</v>
       </c>
     </row>
     <row r="390">
@@ -9038,13 +9170,13 @@
         <v>0.12918858989485416</v>
       </c>
       <c r="C390" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D390" t="s">
-        <v>649</v>
+        <v>426</v>
       </c>
       <c r="E390" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
     </row>
     <row r="391">
@@ -9055,13 +9187,13 @@
         <v>0.12405715306546573</v>
       </c>
       <c r="C391" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D391" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="E391" t="s">
-        <v>783</v>
+        <v>828</v>
       </c>
     </row>
     <row r="392">
@@ -9075,10 +9207,10 @@
         <v>407</v>
       </c>
       <c r="D392" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E392" t="s">
-        <v>412</v>
+        <v>712</v>
       </c>
     </row>
     <row r="393">
@@ -9089,13 +9221,13 @@
         <v>0.11177869655205011</v>
       </c>
       <c r="C393" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="D393" t="s">
-        <v>422</v>
+        <v>654</v>
       </c>
       <c r="E393" t="s">
-        <v>784</v>
+        <v>654</v>
       </c>
     </row>
     <row r="394">
@@ -9109,10 +9241,10 @@
         <v>407</v>
       </c>
       <c r="D394" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E394" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="395">
@@ -9126,10 +9258,10 @@
         <v>407</v>
       </c>
       <c r="D395" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E395" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="396">
@@ -9143,10 +9275,10 @@
         <v>407</v>
       </c>
       <c r="D396" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="E396" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
     </row>
     <row r="397">
@@ -9160,10 +9292,10 @@
         <v>407</v>
       </c>
       <c r="D397" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="E397" t="s">
-        <v>785</v>
+        <v>829</v>
       </c>
     </row>
   </sheetData>
